--- a/output/Tables/2019/Resampling/HIA_per_age.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age.xlsx
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>2.205</v>
+        <v>2.473</v>
       </c>
       <c r="D16">
-        <v>1.103</v>
+        <v>1.467</v>
       </c>
       <c r="E16">
-        <v>3.528</v>
+        <v>3.481</v>
       </c>
       <c r="F16">
-        <v>9.635</v>
+        <v>10.822</v>
       </c>
       <c r="G16">
-        <v>4.784</v>
+        <v>6.355</v>
       </c>
       <c r="H16">
-        <v>15.514</v>
+        <v>15.324</v>
       </c>
       <c r="I16">
-        <v>103251.1</v>
+        <v>116045.488</v>
       </c>
       <c r="J16">
-        <v>51772.548</v>
+        <v>68617.251</v>
       </c>
       <c r="K16">
-        <v>165369.959</v>
+        <v>163334.004</v>
       </c>
       <c r="L16">
-        <v>1279948.807</v>
+        <v>1438110.911</v>
       </c>
       <c r="M16">
-        <v>636473.515</v>
+        <v>847079.115</v>
       </c>
       <c r="N16">
-        <v>2062788.428</v>
+        <v>2041353.477</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>66.736</v>
+        <v>74.789</v>
       </c>
       <c r="D17">
-        <v>35.165</v>
+        <v>47.424</v>
       </c>
       <c r="E17">
-        <v>104.206</v>
+        <v>102.116</v>
       </c>
       <c r="F17">
-        <v>256.18</v>
+        <v>286.88</v>
       </c>
       <c r="G17">
-        <v>134.545</v>
+        <v>181.898</v>
       </c>
       <c r="H17">
-        <v>400.088</v>
+        <v>393.117</v>
       </c>
       <c r="I17">
-        <v>3134377.488</v>
+        <v>3514735.199</v>
       </c>
       <c r="J17">
-        <v>1653147.711</v>
+        <v>2227817.447</v>
       </c>
       <c r="K17">
-        <v>4904027.722</v>
+        <v>4804819.301</v>
       </c>
       <c r="L17">
-        <v>34057558.425</v>
+        <v>38189706.865</v>
       </c>
       <c r="M17">
-        <v>17936600.166</v>
+        <v>24198761.535</v>
       </c>
       <c r="N17">
-        <v>53270566.219</v>
+        <v>52268872.241</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>334.306</v>
+        <v>372.396</v>
       </c>
       <c r="D18">
-        <v>187.601</v>
+        <v>253.661</v>
       </c>
       <c r="E18">
-        <v>502.929</v>
+        <v>492.073</v>
       </c>
       <c r="F18">
-        <v>1065.624</v>
+        <v>1186.518</v>
       </c>
       <c r="G18">
-        <v>595.057</v>
+        <v>804.147</v>
       </c>
       <c r="H18">
-        <v>1605.904</v>
+        <v>1570.114</v>
       </c>
       <c r="I18">
-        <v>15712415.269</v>
+        <v>17498233.415</v>
       </c>
       <c r="J18">
-        <v>8809104.988</v>
+        <v>11864658.018</v>
       </c>
       <c r="K18">
-        <v>23632102.05</v>
+        <v>23116930.594</v>
       </c>
       <c r="L18">
-        <v>141726682.304</v>
+        <v>157831233.513</v>
       </c>
       <c r="M18">
-        <v>78992150.19499999</v>
+        <v>106848483.697</v>
       </c>
       <c r="N18">
-        <v>213472840.015</v>
+        <v>208658770.847</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>461.405</v>
+        <v>515.95</v>
       </c>
       <c r="D19">
-        <v>250.821</v>
+        <v>342.97</v>
       </c>
       <c r="E19">
-        <v>705.503</v>
+        <v>687.745</v>
       </c>
       <c r="F19">
-        <v>1144.651</v>
+        <v>1279.421</v>
       </c>
       <c r="G19">
-        <v>620.944</v>
+        <v>850.778</v>
       </c>
       <c r="H19">
-        <v>1746.083</v>
+        <v>1709.355</v>
       </c>
       <c r="I19">
-        <v>21702568.187</v>
+        <v>24250680.28</v>
       </c>
       <c r="J19">
-        <v>11800463.907</v>
+        <v>16205860.891</v>
       </c>
       <c r="K19">
-        <v>33054277.419</v>
+        <v>32290242.001</v>
       </c>
       <c r="L19">
-        <v>152227960.831</v>
+        <v>170046707.427</v>
       </c>
       <c r="M19">
-        <v>82390692.745</v>
+        <v>113218135.411</v>
       </c>
       <c r="N19">
-        <v>232315625.878</v>
+        <v>227217577.422</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>920.772</v>
+        <v>1025.786</v>
       </c>
       <c r="D20">
-        <v>510.536</v>
+        <v>702.561</v>
       </c>
       <c r="E20">
-        <v>1386.574</v>
+        <v>1351.058</v>
       </c>
       <c r="F20">
-        <v>1647.385</v>
+        <v>1834.29</v>
       </c>
       <c r="G20">
-        <v>912.388</v>
+        <v>1249.14</v>
       </c>
       <c r="H20">
-        <v>2478.42</v>
+        <v>2424.634</v>
       </c>
       <c r="I20">
-        <v>43250003.333</v>
+        <v>48192101.767</v>
       </c>
       <c r="J20">
-        <v>24072822.057</v>
+        <v>32897512.427</v>
       </c>
       <c r="K20">
-        <v>65100961.785</v>
+        <v>63513647.653</v>
       </c>
       <c r="L20">
-        <v>219027310.892</v>
+        <v>244114114.485</v>
       </c>
       <c r="M20">
-        <v>121412314.501</v>
+        <v>165816476.689</v>
       </c>
       <c r="N20">
-        <v>330027746.064</v>
+        <v>322273215.345</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>1137.139</v>
+        <v>1270.239</v>
       </c>
       <c r="D21">
-        <v>627.162</v>
+        <v>865.833</v>
       </c>
       <c r="E21">
-        <v>1716.769</v>
+        <v>1674.724</v>
       </c>
       <c r="F21">
-        <v>1278.868</v>
+        <v>1428.117</v>
       </c>
       <c r="G21">
-        <v>708.977</v>
+        <v>976.288</v>
       </c>
       <c r="H21">
-        <v>1930.935</v>
+        <v>1881.488</v>
       </c>
       <c r="I21">
-        <v>53378808.914</v>
+        <v>59667002.675</v>
       </c>
       <c r="J21">
-        <v>29459938.766</v>
+        <v>40733813.773</v>
       </c>
       <c r="K21">
-        <v>80759286.78399999</v>
+        <v>78571081.11300001</v>
       </c>
       <c r="L21">
-        <v>169985733.736</v>
+        <v>189799337.804</v>
       </c>
       <c r="M21">
-        <v>93956624.906</v>
+        <v>129579085.053</v>
       </c>
       <c r="N21">
-        <v>257080213.266</v>
+        <v>250340660.073</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>639.794</v>
+        <v>716.4109999999999</v>
       </c>
       <c r="D22">
-        <v>355.664</v>
+        <v>502.97</v>
       </c>
       <c r="E22">
-        <v>965.222</v>
+        <v>929.567</v>
       </c>
       <c r="F22">
-        <v>219.098</v>
+        <v>246.078</v>
       </c>
       <c r="G22">
-        <v>118.655</v>
+        <v>167.653</v>
       </c>
       <c r="H22">
-        <v>336.545</v>
+        <v>325.373</v>
       </c>
       <c r="I22">
-        <v>30056971.44</v>
+        <v>33625799.363</v>
       </c>
       <c r="J22">
-        <v>16710131.003</v>
+        <v>23630741.804</v>
       </c>
       <c r="K22">
-        <v>45336193.471</v>
+        <v>43647073.811</v>
       </c>
       <c r="L22">
-        <v>29142413.411</v>
+        <v>32741328.45</v>
       </c>
       <c r="M22">
-        <v>15796646.801</v>
+        <v>22221812.901</v>
       </c>
       <c r="N22">
-        <v>44813693.496</v>
+        <v>43248118.786</v>
       </c>
     </row>
     <row r="23">
@@ -2463,13 +2463,13 @@
         <v>23116.076</v>
       </c>
       <c r="F44">
-        <v>170487.535</v>
+        <v>28414.589</v>
       </c>
       <c r="G44">
-        <v>100657.831</v>
+        <v>16776.305</v>
       </c>
       <c r="H44">
-        <v>252949.228</v>
+        <v>42158.205</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>22660048983.454</v>
+        <v>3776674830.576</v>
       </c>
       <c r="M44">
-        <v>13433056751.131</v>
+        <v>2238842791.855</v>
       </c>
       <c r="N44">
-        <v>33658262729.229</v>
+        <v>5609710454.872</v>
       </c>
     </row>
     <row r="45">
@@ -2511,13 +2511,13 @@
         <v>51332.483</v>
       </c>
       <c r="F45">
-        <v>342272.959</v>
+        <v>57045.493</v>
       </c>
       <c r="G45">
-        <v>214876.992</v>
+        <v>35812.832</v>
       </c>
       <c r="H45">
-        <v>493564.593</v>
+        <v>82260.766</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>45538769205.404</v>
+        <v>7589794867.567</v>
       </c>
       <c r="M45">
-        <v>28524575690.677</v>
+        <v>4754095948.446</v>
       </c>
       <c r="N45">
-        <v>65458145470.482</v>
+        <v>10909690911.747</v>
       </c>
     </row>
     <row r="46">
@@ -2559,13 +2559,13 @@
         <v>60415.728</v>
       </c>
       <c r="F46">
-        <v>327432.051</v>
+        <v>54572.009</v>
       </c>
       <c r="G46">
-        <v>203996.73</v>
+        <v>33999.455</v>
       </c>
       <c r="H46">
-        <v>471197.975</v>
+        <v>78532.996</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>43561943399.991</v>
+        <v>7260323899.998</v>
       </c>
       <c r="M46">
-        <v>27162612741.547</v>
+        <v>4527102123.591</v>
       </c>
       <c r="N46">
-        <v>62750582211.056</v>
+        <v>10458430368.509</v>
       </c>
     </row>
     <row r="47">
@@ -2607,13 +2607,13 @@
         <v>34878.914</v>
       </c>
       <c r="F47">
-        <v>146889.903</v>
+        <v>24481.651</v>
       </c>
       <c r="G47">
-        <v>92518.97</v>
+        <v>15419.828</v>
       </c>
       <c r="H47">
-        <v>210563.209</v>
+        <v>35093.868</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>19536579272.025</v>
+        <v>3256096545.338</v>
       </c>
       <c r="M47">
-        <v>12252552301.33</v>
+        <v>2042092050.222</v>
       </c>
       <c r="N47">
-        <v>28066235340.45</v>
+        <v>4677705890.075</v>
       </c>
     </row>
     <row r="48">
@@ -2655,13 +2655,13 @@
         <v>51945.667</v>
       </c>
       <c r="F48">
-        <v>158075.348</v>
+        <v>26345.891</v>
       </c>
       <c r="G48">
-        <v>101719.78</v>
+        <v>16953.297</v>
       </c>
       <c r="H48">
-        <v>224502.534</v>
+        <v>37417.089</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>20998839125.656</v>
+        <v>3499806520.943</v>
       </c>
       <c r="M48">
-        <v>13468372971.094</v>
+        <v>2244728828.516</v>
       </c>
       <c r="N48">
-        <v>29888794883.124</v>
+        <v>4981465813.854</v>
       </c>
     </row>
     <row r="49">
@@ -2703,13 +2703,13 @@
         <v>30869.333</v>
       </c>
       <c r="F49">
-        <v>57602.885</v>
+        <v>9600.481</v>
       </c>
       <c r="G49">
-        <v>37073.42</v>
+        <v>6178.903</v>
       </c>
       <c r="H49">
-        <v>81589.018</v>
+        <v>13598.17</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>7660806403.556</v>
+        <v>1276801067.259</v>
       </c>
       <c r="M49">
-        <v>4924427563.292</v>
+        <v>820737927.215</v>
       </c>
       <c r="N49">
-        <v>10844489868.463</v>
+        <v>1807414978.077</v>
       </c>
     </row>
     <row r="50">

--- a/output/Tables/2019/Resampling/HIA_per_age.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age.xlsx
@@ -447,13 +447,13 @@
         <v>147.353</v>
       </c>
       <c r="F2">
-        <v>6265.129</v>
+        <v>1044.188</v>
       </c>
       <c r="G2">
-        <v>3980.872</v>
+        <v>663.479</v>
       </c>
       <c r="H2">
-        <v>8770.909</v>
+        <v>1461.818</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>833315429.704</v>
+        <v>138885904.951</v>
       </c>
       <c r="M2">
-        <v>529294779.739</v>
+        <v>88215796.623</v>
       </c>
       <c r="N2">
-        <v>1166983985.427</v>
+        <v>194497330.904</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>371.353</v>
       </c>
       <c r="F3">
-        <v>14089.469</v>
+        <v>2348.245</v>
       </c>
       <c r="G3">
-        <v>9388.695</v>
+        <v>1564.782</v>
       </c>
       <c r="H3">
-        <v>19229.522</v>
+        <v>3204.92</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1873771833.115</v>
+        <v>312295305.519</v>
       </c>
       <c r="M3">
-        <v>1247650483.221</v>
+        <v>207941747.204</v>
       </c>
       <c r="N3">
-        <v>2563438578.609</v>
+        <v>427239763.101</v>
       </c>
     </row>
     <row r="4">
@@ -543,13 +543,13 @@
         <v>1188.979</v>
       </c>
       <c r="F4">
-        <v>35124.693</v>
+        <v>5854.116</v>
       </c>
       <c r="G4">
-        <v>22701.17</v>
+        <v>3783.528</v>
       </c>
       <c r="H4">
-        <v>48793.519</v>
+        <v>8132.253</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>4679091756.896</v>
+        <v>779848626.149</v>
       </c>
       <c r="M4">
-        <v>3014599172.439</v>
+        <v>502433195.407</v>
       </c>
       <c r="N4">
-        <v>6511178741.551</v>
+        <v>1085196456.925</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>2072.692</v>
       </c>
       <c r="F5">
-        <v>47466.302</v>
+        <v>7911.05</v>
       </c>
       <c r="G5">
-        <v>31189.644</v>
+        <v>5198.274</v>
       </c>
       <c r="H5">
-        <v>65336.785</v>
+        <v>10889.464</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6313076323.554</v>
+        <v>1052179387.259</v>
       </c>
       <c r="M5">
-        <v>4140944167.064</v>
+        <v>690157361.177</v>
       </c>
       <c r="N5">
-        <v>8685276041.774</v>
+        <v>1447546006.962</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>6256.746</v>
       </c>
       <c r="F6">
-        <v>100430.304</v>
+        <v>16738.384</v>
       </c>
       <c r="G6">
-        <v>68859.19500000001</v>
+        <v>11476.533</v>
       </c>
       <c r="H6">
-        <v>135310.574</v>
+        <v>22551.762</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>13354453870.499</v>
+        <v>2225742311.75</v>
       </c>
       <c r="M6">
-        <v>9158323754.497</v>
+        <v>1526387292.416</v>
       </c>
       <c r="N6">
-        <v>17974393182.136</v>
+        <v>2995732197.023</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         <v>12143.782</v>
       </c>
       <c r="F7">
-        <v>103721.316</v>
+        <v>17286.886</v>
       </c>
       <c r="G7">
-        <v>71256.033</v>
+        <v>11876.006</v>
       </c>
       <c r="H7">
-        <v>139463.681</v>
+        <v>23243.947</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>13783749064.133</v>
+        <v>2297291510.689</v>
       </c>
       <c r="M7">
-        <v>9482339824.164</v>
+        <v>1580389970.694</v>
       </c>
       <c r="N7">
-        <v>18520793695.362</v>
+        <v>3086798949.227</v>
       </c>
     </row>
     <row r="8">
@@ -735,13 +735,13 @@
         <v>28141.84</v>
       </c>
       <c r="F8">
-        <v>36020.284</v>
+        <v>6003.381</v>
       </c>
       <c r="G8">
-        <v>24084.596</v>
+        <v>4014.099</v>
       </c>
       <c r="H8">
-        <v>49146.919</v>
+        <v>8191.153</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>4788356875.14</v>
+        <v>798059479.1900001</v>
       </c>
       <c r="M8">
-        <v>3201667355.413</v>
+        <v>533611225.902</v>
       </c>
       <c r="N8">
-        <v>6536020552.57</v>
+        <v>1089336758.762</v>
       </c>
     </row>
     <row r="9">
@@ -783,31 +783,31 @@
         <v>44.643</v>
       </c>
       <c r="F9">
-        <v>92.259</v>
+        <v>19.004</v>
       </c>
       <c r="G9">
-        <v>49.83</v>
+        <v>10.252</v>
       </c>
       <c r="H9">
-        <v>144.914</v>
+        <v>29.839</v>
       </c>
       <c r="I9">
-        <v>595465.773</v>
+        <v>1584135.757</v>
       </c>
       <c r="J9">
-        <v>321464.636</v>
+        <v>855202.175</v>
       </c>
       <c r="K9">
-        <v>933586.932</v>
+        <v>2483649.79</v>
       </c>
       <c r="L9">
-        <v>12269254.786</v>
+        <v>2528315.894</v>
       </c>
       <c r="M9">
-        <v>6638958.368</v>
+        <v>1366622.1</v>
       </c>
       <c r="N9">
-        <v>19238971.984</v>
+        <v>3957706.677</v>
       </c>
     </row>
     <row r="10">
@@ -831,31 +831,31 @@
         <v>111.895</v>
       </c>
       <c r="F10">
-        <v>207.404</v>
+        <v>42.689</v>
       </c>
       <c r="G10">
-        <v>116.037</v>
+        <v>23.9</v>
       </c>
       <c r="H10">
-        <v>316.374</v>
+        <v>65.137</v>
       </c>
       <c r="I10">
-        <v>1539936.502</v>
+        <v>4096740.045</v>
       </c>
       <c r="J10">
-        <v>862675.733</v>
+        <v>2295002.564</v>
       </c>
       <c r="K10">
-        <v>2351038.196</v>
+        <v>6254538.618</v>
       </c>
       <c r="L10">
-        <v>27582624.274</v>
+        <v>5678414.587</v>
       </c>
       <c r="M10">
-        <v>15454296.273</v>
+        <v>3180493.923</v>
       </c>
       <c r="N10">
-        <v>42005334.303</v>
+        <v>8648060.064999999</v>
       </c>
     </row>
     <row r="11">
@@ -879,31 +879,31 @@
         <v>407.777</v>
       </c>
       <c r="F11">
-        <v>579.489</v>
+        <v>119.298</v>
       </c>
       <c r="G11">
-        <v>316.448</v>
+        <v>65.172</v>
       </c>
       <c r="H11">
-        <v>901.273</v>
+        <v>185.628</v>
       </c>
       <c r="I11">
-        <v>5465408.111</v>
+        <v>14539791.89</v>
       </c>
       <c r="J11">
-        <v>2968634.056</v>
+        <v>7897547.72</v>
       </c>
       <c r="K11">
-        <v>8544903.909</v>
+        <v>22732268.484</v>
       </c>
       <c r="L11">
-        <v>77023012.81200001</v>
+        <v>15852215.657</v>
       </c>
       <c r="M11">
-        <v>42169181.561</v>
+        <v>8672479.662</v>
       </c>
       <c r="N11">
-        <v>119695340.328</v>
+        <v>24673858.743</v>
       </c>
     </row>
     <row r="12">
@@ -927,31 +927,31 @@
         <v>884.431</v>
       </c>
       <c r="F12">
-        <v>969.043</v>
+        <v>199.533</v>
       </c>
       <c r="G12">
-        <v>538.268</v>
+        <v>110.762</v>
       </c>
       <c r="H12">
-        <v>1494.348</v>
+        <v>307.445</v>
       </c>
       <c r="I12">
-        <v>12030122.192</v>
+        <v>32004100.982</v>
       </c>
       <c r="J12">
-        <v>6670364.366</v>
+        <v>17745373.766</v>
       </c>
       <c r="K12">
-        <v>18507285.562</v>
+        <v>49235496.246</v>
       </c>
       <c r="L12">
-        <v>128862866.826</v>
+        <v>26527836.692</v>
       </c>
       <c r="M12">
-        <v>71725644.594</v>
+        <v>14730922.656</v>
       </c>
       <c r="N12">
-        <v>198183805.822</v>
+        <v>40811298.333</v>
       </c>
     </row>
     <row r="13">
@@ -975,31 +975,31 @@
         <v>3201.941</v>
       </c>
       <c r="F13">
-        <v>2489.646</v>
+        <v>512.673</v>
       </c>
       <c r="G13">
-        <v>1445.392</v>
+        <v>297.551</v>
       </c>
       <c r="H13">
-        <v>3720.949</v>
+        <v>766.425</v>
       </c>
       <c r="I13">
-        <v>44906781.216</v>
+        <v>119466879.706</v>
       </c>
       <c r="J13">
-        <v>26274075.59</v>
+        <v>69897724.64</v>
       </c>
       <c r="K13">
-        <v>66951825.187</v>
+        <v>178113982.548</v>
       </c>
       <c r="L13">
-        <v>331317495.141</v>
+        <v>68222100.41500001</v>
       </c>
       <c r="M13">
-        <v>192611580.873</v>
+        <v>39662525.4</v>
       </c>
       <c r="N13">
-        <v>495248911.499</v>
+        <v>101995498.273</v>
       </c>
     </row>
     <row r="14">
@@ -1023,31 +1023,31 @@
         <v>5412.612</v>
       </c>
       <c r="F14">
-        <v>2421.636</v>
+        <v>498.561</v>
       </c>
       <c r="G14">
-        <v>1408.249</v>
+        <v>289.661</v>
       </c>
       <c r="H14">
-        <v>3615.553</v>
+        <v>743.985</v>
       </c>
       <c r="I14">
-        <v>75936811.008</v>
+        <v>202017014.366</v>
       </c>
       <c r="J14">
-        <v>44033785.633</v>
+        <v>117144422.931</v>
       </c>
       <c r="K14">
-        <v>113512906.716</v>
+        <v>301981847.832</v>
       </c>
       <c r="L14">
-        <v>321815248.417</v>
+        <v>66270202.803</v>
       </c>
       <c r="M14">
-        <v>186990376.487</v>
+        <v>38460212.152</v>
       </c>
       <c r="N14">
-        <v>481349173.691</v>
+        <v>99110109.619</v>
       </c>
     </row>
     <row r="15">
@@ -1071,31 +1071,31 @@
         <v>5574.494</v>
       </c>
       <c r="F15">
-        <v>588.251</v>
+        <v>121.132</v>
       </c>
       <c r="G15">
-        <v>317.629</v>
+        <v>65.474</v>
       </c>
       <c r="H15">
-        <v>915.853</v>
+        <v>188.479</v>
       </c>
       <c r="I15">
-        <v>76639388.333</v>
+        <v>203886102.25</v>
       </c>
       <c r="J15">
-        <v>43233941.647</v>
+        <v>115016573.579</v>
       </c>
       <c r="K15">
-        <v>116409487.098</v>
+        <v>309687708.965</v>
       </c>
       <c r="L15">
-        <v>78181258.568</v>
+        <v>16096085.861</v>
       </c>
       <c r="M15">
-        <v>42344702.764</v>
+        <v>8729641.296</v>
       </c>
       <c r="N15">
-        <v>121681044.267</v>
+        <v>25031031.94</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>2.473</v>
+        <v>0.467</v>
       </c>
       <c r="D16">
-        <v>1.467</v>
+        <v>0.011</v>
       </c>
       <c r="E16">
-        <v>3.481</v>
+        <v>1.055</v>
       </c>
       <c r="F16">
-        <v>10.822</v>
+        <v>0.348</v>
       </c>
       <c r="G16">
-        <v>6.355</v>
+        <v>0.008</v>
       </c>
       <c r="H16">
-        <v>15.324</v>
+        <v>0.79</v>
       </c>
       <c r="I16">
-        <v>116045.488</v>
+        <v>20554.571</v>
       </c>
       <c r="J16">
-        <v>68617.251</v>
+        <v>468.362</v>
       </c>
       <c r="K16">
-        <v>163334.004</v>
+        <v>46467.716</v>
       </c>
       <c r="L16">
-        <v>1438110.911</v>
+        <v>46203.284</v>
       </c>
       <c r="M16">
-        <v>847079.115</v>
+        <v>1030.941</v>
       </c>
       <c r="N16">
-        <v>2041353.477</v>
+        <v>104742.375</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>74.789</v>
+        <v>14.474</v>
       </c>
       <c r="D17">
-        <v>47.424</v>
+        <v>0.229</v>
       </c>
       <c r="E17">
-        <v>102.116</v>
+        <v>31.812</v>
       </c>
       <c r="F17">
-        <v>286.88</v>
+        <v>9.462</v>
       </c>
       <c r="G17">
-        <v>181.898</v>
+        <v>0.148</v>
       </c>
       <c r="H17">
-        <v>393.117</v>
+        <v>20.899</v>
       </c>
       <c r="I17">
-        <v>3514735.199</v>
+        <v>638004.071</v>
       </c>
       <c r="J17">
-        <v>2227817.447</v>
+        <v>10110.254</v>
       </c>
       <c r="K17">
-        <v>4804819.301</v>
+        <v>1406073.333</v>
       </c>
       <c r="L17">
-        <v>38189706.865</v>
+        <v>1259859.543</v>
       </c>
       <c r="M17">
-        <v>24198761.535</v>
+        <v>19879.603</v>
       </c>
       <c r="N17">
-        <v>52268872.241</v>
+        <v>2780429.242</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>372.396</v>
+        <v>70.262</v>
       </c>
       <c r="D18">
-        <v>253.661</v>
+        <v>1.373</v>
       </c>
       <c r="E18">
-        <v>492.073</v>
+        <v>152.098</v>
       </c>
       <c r="F18">
-        <v>1186.518</v>
+        <v>38.102</v>
       </c>
       <c r="G18">
-        <v>804.147</v>
+        <v>0.734</v>
       </c>
       <c r="H18">
-        <v>1570.114</v>
+        <v>82.557</v>
       </c>
       <c r="I18">
-        <v>17498233.415</v>
+        <v>3099113.282</v>
       </c>
       <c r="J18">
-        <v>11864658.018</v>
+        <v>61124.972</v>
       </c>
       <c r="K18">
-        <v>23116930.594</v>
+        <v>6706167.37</v>
       </c>
       <c r="L18">
-        <v>157831233.513</v>
+        <v>5075938.066</v>
       </c>
       <c r="M18">
-        <v>106848483.697</v>
+        <v>98145.505</v>
       </c>
       <c r="N18">
-        <v>208658770.847</v>
+        <v>11021792.44</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>515.95</v>
+        <v>98.146</v>
       </c>
       <c r="D19">
-        <v>342.97</v>
+        <v>2.096</v>
       </c>
       <c r="E19">
-        <v>687.745</v>
+        <v>212.406</v>
       </c>
       <c r="F19">
-        <v>1279.421</v>
+        <v>41.382</v>
       </c>
       <c r="G19">
-        <v>850.778</v>
+        <v>0.891</v>
       </c>
       <c r="H19">
-        <v>1709.355</v>
+        <v>90.002</v>
       </c>
       <c r="I19">
-        <v>24250680.28</v>
+        <v>4325248.872</v>
       </c>
       <c r="J19">
-        <v>16205860.891</v>
+        <v>91478.804</v>
       </c>
       <c r="K19">
-        <v>32290242.001</v>
+        <v>9383529.988</v>
       </c>
       <c r="L19">
-        <v>170046707.427</v>
+        <v>5500152.964</v>
       </c>
       <c r="M19">
-        <v>113218135.411</v>
+        <v>119086.77</v>
       </c>
       <c r="N19">
-        <v>227217577.422</v>
+        <v>11936714.201</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>1025.786</v>
+        <v>197.027</v>
       </c>
       <c r="D20">
-        <v>702.561</v>
+        <v>3.166</v>
       </c>
       <c r="E20">
-        <v>1351.058</v>
+        <v>426.477</v>
       </c>
       <c r="F20">
-        <v>1834.29</v>
+        <v>59.967</v>
       </c>
       <c r="G20">
-        <v>1249.14</v>
+        <v>0.966</v>
       </c>
       <c r="H20">
-        <v>2424.634</v>
+        <v>129.788</v>
       </c>
       <c r="I20">
-        <v>48192101.767</v>
+        <v>8696722.370999999</v>
       </c>
       <c r="J20">
-        <v>32897512.427</v>
+        <v>138699.496</v>
       </c>
       <c r="K20">
-        <v>63513647.653</v>
+        <v>18748487.971</v>
       </c>
       <c r="L20">
-        <v>244114114.485</v>
+        <v>7968511.67</v>
       </c>
       <c r="M20">
-        <v>165816476.689</v>
+        <v>130499.029</v>
       </c>
       <c r="N20">
-        <v>322273215.345</v>
+        <v>17282947.045</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>1270.239</v>
+        <v>247.096</v>
       </c>
       <c r="D21">
-        <v>865.833</v>
+        <v>4.133</v>
       </c>
       <c r="E21">
-        <v>1674.724</v>
+        <v>533.022</v>
       </c>
       <c r="F21">
-        <v>1428.117</v>
+        <v>47.337</v>
       </c>
       <c r="G21">
-        <v>976.288</v>
+        <v>0.803</v>
       </c>
       <c r="H21">
-        <v>1881.488</v>
+        <v>101.906</v>
       </c>
       <c r="I21">
-        <v>59667002.675</v>
+        <v>10899948.904</v>
       </c>
       <c r="J21">
-        <v>40733813.773</v>
+        <v>180464.276</v>
       </c>
       <c r="K21">
-        <v>78571081.11300001</v>
+        <v>23516330.138</v>
       </c>
       <c r="L21">
-        <v>189799337.804</v>
+        <v>6297546.723</v>
       </c>
       <c r="M21">
-        <v>129579085.053</v>
+        <v>105239.249</v>
       </c>
       <c r="N21">
-        <v>250340660.073</v>
+        <v>13564934.711</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>716.4109999999999</v>
+        <v>137.084</v>
       </c>
       <c r="D22">
-        <v>502.97</v>
+        <v>3.642</v>
       </c>
       <c r="E22">
-        <v>929.567</v>
+        <v>290.899</v>
       </c>
       <c r="F22">
-        <v>246.078</v>
+        <v>8.074</v>
       </c>
       <c r="G22">
-        <v>167.653</v>
+        <v>0.199</v>
       </c>
       <c r="H22">
-        <v>325.373</v>
+        <v>17.399</v>
       </c>
       <c r="I22">
-        <v>33625799.363</v>
+        <v>6045192.293</v>
       </c>
       <c r="J22">
-        <v>23630741.804</v>
+        <v>161319.524</v>
       </c>
       <c r="K22">
-        <v>43647073.811</v>
+        <v>12811626.869</v>
       </c>
       <c r="L22">
-        <v>32741328.45</v>
+        <v>1074188.379</v>
       </c>
       <c r="M22">
-        <v>22221812.901</v>
+        <v>26214.597</v>
       </c>
       <c r="N22">
-        <v>43248118.786</v>
+        <v>2315381.838</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>12.28</v>
+        <v>12.27</v>
       </c>
       <c r="D23">
         <v>0.281</v>
       </c>
       <c r="E23">
-        <v>27.003</v>
+        <v>26.964</v>
       </c>
       <c r="F23">
-        <v>42.338</v>
+        <v>7.053</v>
       </c>
       <c r="G23">
-        <v>0.962</v>
+        <v>0.161</v>
       </c>
       <c r="H23">
-        <v>93.02800000000001</v>
+        <v>15.523</v>
       </c>
       <c r="I23">
-        <v>181816.336</v>
+        <v>181853.462</v>
       </c>
       <c r="J23">
-        <v>4173.762</v>
+        <v>4168.398</v>
       </c>
       <c r="K23">
-        <v>399626.949</v>
+        <v>398959.379</v>
       </c>
       <c r="L23">
-        <v>5638089.761</v>
+        <v>938778.714</v>
       </c>
       <c r="M23">
-        <v>127826.993</v>
+        <v>21243.003</v>
       </c>
       <c r="N23">
-        <v>12399509.038</v>
+        <v>2069038.434</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>75.94</v>
+        <v>75.983</v>
       </c>
       <c r="D24">
         <v>1.241</v>
       </c>
       <c r="E24">
-        <v>163.723</v>
+        <v>163.473</v>
       </c>
       <c r="F24">
-        <v>230.83</v>
+        <v>38.558</v>
       </c>
       <c r="G24">
-        <v>3.738</v>
+        <v>0.627</v>
       </c>
       <c r="H24">
-        <v>497.999</v>
+        <v>82.836</v>
       </c>
       <c r="I24">
-        <v>1125995.448</v>
+        <v>1123468.99</v>
       </c>
       <c r="J24">
-        <v>18036.05</v>
+        <v>18377.971</v>
       </c>
       <c r="K24">
-        <v>2424042.745</v>
+        <v>2419882.012</v>
       </c>
       <c r="L24">
-        <v>30805041.663</v>
+        <v>5126630.194</v>
       </c>
       <c r="M24">
-        <v>490838.625</v>
+        <v>83733.766</v>
       </c>
       <c r="N24">
-        <v>66382883.244</v>
+        <v>11055361.778</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>244.546</v>
+        <v>244.783</v>
       </c>
       <c r="D25">
-        <v>4.759</v>
+        <v>4.819</v>
       </c>
       <c r="E25">
-        <v>532.1420000000001</v>
+        <v>532.879</v>
       </c>
       <c r="F25">
-        <v>600.566</v>
+        <v>100.099</v>
       </c>
       <c r="G25">
-        <v>11.62</v>
+        <v>1.967</v>
       </c>
       <c r="H25">
-        <v>1301.171</v>
+        <v>217.486</v>
       </c>
       <c r="I25">
-        <v>3627458.727</v>
+        <v>3625475.743</v>
       </c>
       <c r="J25">
-        <v>71181.174</v>
+        <v>70834.727</v>
       </c>
       <c r="K25">
-        <v>7871457.7</v>
+        <v>7878520.857</v>
       </c>
       <c r="L25">
-        <v>79855050.243</v>
+        <v>13298365.372</v>
       </c>
       <c r="M25">
-        <v>1534927.049</v>
+        <v>260240.805</v>
       </c>
       <c r="N25">
-        <v>172759020.806</v>
+        <v>28959434.772</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>404.316</v>
+        <v>404.553</v>
       </c>
       <c r="D26">
-        <v>8.513</v>
+        <v>8.571</v>
       </c>
       <c r="E26">
-        <v>871.481</v>
+        <v>869.501</v>
       </c>
       <c r="F26">
-        <v>747.075</v>
+        <v>124.441</v>
       </c>
       <c r="G26">
-        <v>15.771</v>
+        <v>2.632</v>
       </c>
       <c r="H26">
-        <v>1610.88</v>
+        <v>268.455</v>
       </c>
       <c r="I26">
-        <v>5965948.499</v>
+        <v>5975195.907</v>
       </c>
       <c r="J26">
-        <v>125271.218</v>
+        <v>127210.737</v>
       </c>
       <c r="K26">
-        <v>12859385.714</v>
+        <v>12872608.872</v>
       </c>
       <c r="L26">
-        <v>99375849.36399999</v>
+        <v>16560898.807</v>
       </c>
       <c r="M26">
-        <v>2120177.019</v>
+        <v>358261.704</v>
       </c>
       <c r="N26">
-        <v>214496334.033</v>
+        <v>35599321.398</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>1415.845</v>
+        <v>1415.376</v>
       </c>
       <c r="D27">
-        <v>19.367</v>
+        <v>19.559</v>
       </c>
       <c r="E27">
-        <v>3018.282</v>
+        <v>3018.289</v>
       </c>
       <c r="F27">
-        <v>1755.188</v>
+        <v>292.816</v>
       </c>
       <c r="G27">
-        <v>24.983</v>
+        <v>4.13</v>
       </c>
       <c r="H27">
-        <v>3756.175</v>
+        <v>625.5069999999999</v>
       </c>
       <c r="I27">
-        <v>20951661.401</v>
+        <v>20982325.568</v>
       </c>
       <c r="J27">
-        <v>290361.259</v>
+        <v>288163.25</v>
       </c>
       <c r="K27">
-        <v>44786094.968</v>
+        <v>44589518.674</v>
       </c>
       <c r="L27">
-        <v>233782878.166</v>
+        <v>38939637.511</v>
       </c>
       <c r="M27">
-        <v>3315164.762</v>
+        <v>548370.599</v>
       </c>
       <c r="N27">
-        <v>498903674.32</v>
+        <v>82953429.11499999</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>1547.505</v>
+        <v>1548.372</v>
       </c>
       <c r="D28">
-        <v>24.163</v>
+        <v>24.279</v>
       </c>
       <c r="E28">
-        <v>3273.177</v>
+        <v>3271.512</v>
       </c>
       <c r="F28">
-        <v>1125.792</v>
+        <v>187.558</v>
       </c>
       <c r="G28">
-        <v>17.873</v>
+        <v>2.965</v>
       </c>
       <c r="H28">
-        <v>2380.059</v>
+        <v>397.039</v>
       </c>
       <c r="I28">
-        <v>22910327.429</v>
+        <v>22870939.064</v>
       </c>
       <c r="J28">
-        <v>357098.369</v>
+        <v>354637.753</v>
       </c>
       <c r="K28">
-        <v>48357763.807</v>
+        <v>48486117.682</v>
       </c>
       <c r="L28">
-        <v>149540485.948</v>
+        <v>24919803.941</v>
       </c>
       <c r="M28">
-        <v>2403788.575</v>
+        <v>399107.922</v>
       </c>
       <c r="N28">
-        <v>315983350.885</v>
+        <v>52732601.913</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>1110.04</v>
+        <v>1110.284</v>
       </c>
       <c r="D29">
-        <v>27.65</v>
+        <v>27.785</v>
       </c>
       <c r="E29">
-        <v>2356.185</v>
+        <v>2349.741</v>
       </c>
       <c r="F29">
-        <v>193.216</v>
+        <v>32.238</v>
       </c>
       <c r="G29">
-        <v>4.722</v>
+        <v>0.797</v>
       </c>
       <c r="H29">
-        <v>417.981</v>
+        <v>69.73</v>
       </c>
       <c r="I29">
-        <v>16429984.197</v>
+        <v>16450196.852</v>
       </c>
       <c r="J29">
-        <v>410065.028</v>
+        <v>411318.542</v>
       </c>
       <c r="K29">
-        <v>34837255.318</v>
+        <v>34847807.536</v>
       </c>
       <c r="L29">
-        <v>25685052.356</v>
+        <v>4281199.096</v>
       </c>
       <c r="M29">
-        <v>630563.389</v>
+        <v>103702.421</v>
       </c>
       <c r="N29">
-        <v>55632723.288</v>
+        <v>9242259.648</v>
       </c>
     </row>
     <row r="30">
@@ -1782,40 +1782,40 @@
         </is>
       </c>
       <c r="C30">
-        <v>43.957</v>
+        <v>43.948</v>
       </c>
       <c r="D30">
-        <v>-0.006</v>
+        <v>-0.011</v>
       </c>
       <c r="E30">
-        <v>91.75700000000001</v>
+        <v>91.819</v>
       </c>
       <c r="F30">
-        <v>184.794</v>
+        <v>31.254</v>
       </c>
       <c r="G30">
-        <v>-0.094</v>
+        <v>-0.017</v>
       </c>
       <c r="H30">
-        <v>386.927</v>
+        <v>65.389</v>
       </c>
       <c r="I30">
-        <v>1607055.109</v>
+        <v>3306237.049</v>
       </c>
       <c r="J30">
-        <v>-435.504</v>
+        <v>-468.988</v>
       </c>
       <c r="K30">
-        <v>3358574.745</v>
+        <v>6897293.319</v>
       </c>
       <c r="L30">
-        <v>24577714.649</v>
+        <v>4152064.752</v>
       </c>
       <c r="M30">
-        <v>-3530.762</v>
+        <v>-958.372</v>
       </c>
       <c r="N30">
-        <v>51594949.608</v>
+        <v>8700105.348999999</v>
       </c>
     </row>
     <row r="31">
@@ -1830,40 +1830,40 @@
         </is>
       </c>
       <c r="C31">
-        <v>138.456</v>
+        <v>138.433</v>
       </c>
       <c r="D31">
-        <v>1.714</v>
+        <v>1.74</v>
       </c>
       <c r="E31">
-        <v>280.853</v>
+        <v>281.176</v>
       </c>
       <c r="F31">
-        <v>512.426</v>
+        <v>86.25</v>
       </c>
       <c r="G31">
-        <v>6.463</v>
+        <v>1.084</v>
       </c>
       <c r="H31">
-        <v>1037.019</v>
+        <v>175.668</v>
       </c>
       <c r="I31">
-        <v>5050571.142</v>
+        <v>10419315.711</v>
       </c>
       <c r="J31">
-        <v>63530.543</v>
+        <v>125724.873</v>
       </c>
       <c r="K31">
-        <v>10264447.5</v>
+        <v>21140888.573</v>
       </c>
       <c r="L31">
-        <v>68052066.72400001</v>
+        <v>11499763.91</v>
       </c>
       <c r="M31">
-        <v>831469.708</v>
+        <v>147416.079</v>
       </c>
       <c r="N31">
-        <v>137897718.435</v>
+        <v>23358217.529</v>
       </c>
     </row>
     <row r="32">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>410.417</v>
+        <v>411.126</v>
       </c>
       <c r="D32">
-        <v>0.025</v>
+        <v>0.073</v>
       </c>
       <c r="E32">
-        <v>847.006</v>
+        <v>847.063</v>
       </c>
       <c r="F32">
-        <v>1210.598</v>
+        <v>204.434</v>
       </c>
       <c r="G32">
-        <v>0.142</v>
+        <v>0.01</v>
       </c>
       <c r="H32">
-        <v>2486.486</v>
+        <v>420.265</v>
       </c>
       <c r="I32">
-        <v>15014047.456</v>
+        <v>30951486.301</v>
       </c>
       <c r="J32">
-        <v>3482.083</v>
+        <v>7479.263</v>
       </c>
       <c r="K32">
-        <v>30846975.897</v>
+        <v>63716433.726</v>
       </c>
       <c r="L32">
-        <v>160874901.104</v>
+        <v>27204734.762</v>
       </c>
       <c r="M32">
-        <v>68104.955</v>
+        <v>-3873.371</v>
       </c>
       <c r="N32">
-        <v>330767100.362</v>
+        <v>55881699.374</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>649.274</v>
+        <v>651.325</v>
       </c>
       <c r="D33">
-        <v>0.331</v>
+        <v>0.487</v>
       </c>
       <c r="E33">
-        <v>1323.845</v>
+        <v>1328.806</v>
       </c>
       <c r="F33">
-        <v>1462.691</v>
+        <v>247.261</v>
       </c>
       <c r="G33">
-        <v>2.675</v>
+        <v>0.182</v>
       </c>
       <c r="H33">
-        <v>2996.469</v>
+        <v>505.606</v>
       </c>
       <c r="I33">
-        <v>23716074.291</v>
+        <v>48865244.887</v>
       </c>
       <c r="J33">
-        <v>23833.66</v>
+        <v>40187.269</v>
       </c>
       <c r="K33">
-        <v>48509643.44</v>
+        <v>99842747.042</v>
       </c>
       <c r="L33">
-        <v>195155220.365</v>
+        <v>32889067.499</v>
       </c>
       <c r="M33">
-        <v>363306.048</v>
+        <v>36394.187</v>
       </c>
       <c r="N33">
-        <v>398275469.76</v>
+        <v>67263168.536</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>2100.035</v>
+        <v>2099.537</v>
       </c>
       <c r="D34">
-        <v>-6.711</v>
+        <v>-6.599</v>
       </c>
       <c r="E34">
-        <v>4154.865</v>
+        <v>4152.235</v>
       </c>
       <c r="F34">
-        <v>3272.013</v>
+        <v>552.61</v>
       </c>
       <c r="G34">
-        <v>-8.452999999999999</v>
+        <v>-1.061</v>
       </c>
       <c r="H34">
-        <v>6489.231</v>
+        <v>1096.675</v>
       </c>
       <c r="I34">
-        <v>76637211.85600001</v>
+        <v>157857339.75</v>
       </c>
       <c r="J34">
-        <v>-235650.605</v>
+        <v>-527619.5159999999</v>
       </c>
       <c r="K34">
-        <v>151937116.139</v>
+        <v>311766061.526</v>
       </c>
       <c r="L34">
-        <v>435276089.632</v>
+        <v>73466457.40700001</v>
       </c>
       <c r="M34">
-        <v>-1140489.991</v>
+        <v>-166481.042</v>
       </c>
       <c r="N34">
-        <v>862725649.148</v>
+        <v>145663723.143</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>2130.428</v>
+        <v>2130.866</v>
       </c>
       <c r="D35">
-        <v>5.842</v>
+        <v>5.725</v>
       </c>
       <c r="E35">
-        <v>4221.8</v>
+        <v>4214.574</v>
       </c>
       <c r="F35">
-        <v>1931.726</v>
+        <v>326.908</v>
       </c>
       <c r="G35">
-        <v>3.447</v>
+        <v>0.303</v>
       </c>
       <c r="H35">
-        <v>3841.799</v>
+        <v>646.5410000000001</v>
       </c>
       <c r="I35">
-        <v>77801651.67</v>
+        <v>160307266.963</v>
       </c>
       <c r="J35">
-        <v>212231.161</v>
+        <v>446478.101</v>
       </c>
       <c r="K35">
-        <v>154073211.346</v>
+        <v>317492547.894</v>
       </c>
       <c r="L35">
-        <v>257190633.278</v>
+        <v>43485181.057</v>
       </c>
       <c r="M35">
-        <v>247653.729</v>
+        <v>42865.557</v>
       </c>
       <c r="N35">
-        <v>511353680.188</v>
+        <v>86227244.266</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>870.582</v>
+        <v>870.907</v>
       </c>
       <c r="D36">
-        <v>-1.601</v>
+        <v>-1.693</v>
       </c>
       <c r="E36">
-        <v>1760.286</v>
+        <v>1767.203</v>
       </c>
       <c r="F36">
-        <v>181.152</v>
+        <v>30.646</v>
       </c>
       <c r="G36">
-        <v>1.387</v>
+        <v>0.221</v>
       </c>
       <c r="H36">
-        <v>376.37</v>
+        <v>63.559</v>
       </c>
       <c r="I36">
-        <v>31770925.359</v>
+        <v>65416853.911</v>
       </c>
       <c r="J36">
-        <v>-50447.282</v>
+        <v>-75352.402</v>
       </c>
       <c r="K36">
-        <v>64525704.996</v>
+        <v>132774554.068</v>
       </c>
       <c r="L36">
-        <v>24108370.928</v>
+        <v>4066275.991</v>
       </c>
       <c r="M36">
-        <v>192557.557</v>
+        <v>29072.107</v>
       </c>
       <c r="N36">
-        <v>50075092.454</v>
+        <v>8466495.277000001</v>
       </c>
     </row>
     <row r="37">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="C39">
-        <v>2.587</v>
+        <v>2.588</v>
       </c>
       <c r="D39">
-        <v>1.548</v>
+        <v>1.544</v>
       </c>
       <c r="E39">
-        <v>3.824</v>
+        <v>3.831</v>
       </c>
       <c r="F39">
-        <v>16.268</v>
+        <v>3.699</v>
       </c>
       <c r="G39">
-        <v>9.759</v>
+        <v>2.222</v>
       </c>
       <c r="H39">
-        <v>24.026</v>
+        <v>5.466</v>
       </c>
       <c r="I39">
-        <v>58856.946</v>
+        <v>43504.974</v>
       </c>
       <c r="J39">
-        <v>35204.799</v>
+        <v>26054.459</v>
       </c>
       <c r="K39">
-        <v>87111.87</v>
+        <v>64522.588</v>
       </c>
       <c r="L39">
-        <v>2165291.742</v>
+        <v>492016.096</v>
       </c>
       <c r="M39">
-        <v>1299216.46</v>
+        <v>296198.73</v>
       </c>
       <c r="N39">
-        <v>3202313.351</v>
+        <v>728432.848</v>
       </c>
     </row>
     <row r="40">
@@ -2262,40 +2262,40 @@
         </is>
       </c>
       <c r="C40">
-        <v>13.296</v>
+        <v>13.297</v>
       </c>
       <c r="D40">
-        <v>8.246</v>
+        <v>8.263999999999999</v>
       </c>
       <c r="E40">
-        <v>19.231</v>
+        <v>19.311</v>
       </c>
       <c r="F40">
-        <v>66.898</v>
+        <v>15.202</v>
       </c>
       <c r="G40">
-        <v>41.539</v>
+        <v>9.433</v>
       </c>
       <c r="H40">
-        <v>96.801</v>
+        <v>22.024</v>
       </c>
       <c r="I40">
-        <v>302470.539</v>
+        <v>224171.346</v>
       </c>
       <c r="J40">
-        <v>188113.657</v>
+        <v>139132.384</v>
       </c>
       <c r="K40">
-        <v>438692.245</v>
+        <v>324876.072</v>
       </c>
       <c r="L40">
-        <v>8896444.138</v>
+        <v>2022764.903</v>
       </c>
       <c r="M40">
-        <v>5525707.795</v>
+        <v>1255208.248</v>
       </c>
       <c r="N40">
-        <v>12902453.383</v>
+        <v>2927264.371</v>
       </c>
     </row>
     <row r="41">
@@ -2310,40 +2310,40 @@
         </is>
       </c>
       <c r="C41">
-        <v>125.796</v>
+        <v>125.745</v>
       </c>
       <c r="D41">
-        <v>79.871</v>
+        <v>79.995</v>
       </c>
       <c r="E41">
-        <v>180.078</v>
+        <v>179.81</v>
       </c>
       <c r="F41">
-        <v>442.619</v>
+        <v>100.653</v>
       </c>
       <c r="G41">
-        <v>281.101</v>
+        <v>63.626</v>
       </c>
       <c r="H41">
-        <v>634.1180000000001</v>
+        <v>144.263</v>
       </c>
       <c r="I41">
-        <v>2858013.508</v>
+        <v>2115307.958</v>
       </c>
       <c r="J41">
-        <v>1820144.323</v>
+        <v>1348892.35</v>
       </c>
       <c r="K41">
-        <v>4085013.47</v>
+        <v>3025307.241</v>
       </c>
       <c r="L41">
-        <v>58847063.471</v>
+        <v>13386754.572</v>
       </c>
       <c r="M41">
-        <v>37365166.363</v>
+        <v>8490272.562000001</v>
       </c>
       <c r="N41">
-        <v>84380382.707</v>
+        <v>19167130.344</v>
       </c>
     </row>
     <row r="42">
@@ -2358,40 +2358,40 @@
         </is>
       </c>
       <c r="C42">
-        <v>660.742</v>
+        <v>660.67</v>
       </c>
       <c r="D42">
-        <v>420.521</v>
+        <v>421.229</v>
       </c>
       <c r="E42">
-        <v>946.2190000000001</v>
+        <v>946.112</v>
       </c>
       <c r="F42">
-        <v>1391.335</v>
+        <v>316.384</v>
       </c>
       <c r="G42">
-        <v>883.019</v>
+        <v>200.792</v>
       </c>
       <c r="H42">
-        <v>1989.856</v>
+        <v>452.846</v>
       </c>
       <c r="I42">
-        <v>15014552.416</v>
+        <v>11120594.504</v>
       </c>
       <c r="J42">
-        <v>9548801.912</v>
+        <v>7068213.657</v>
       </c>
       <c r="K42">
-        <v>21481231.189</v>
+        <v>15917096.396</v>
       </c>
       <c r="L42">
-        <v>184842051.962</v>
+        <v>42035060.187</v>
       </c>
       <c r="M42">
-        <v>117575949.524</v>
+        <v>26711276.33</v>
       </c>
       <c r="N42">
-        <v>264694906.893</v>
+        <v>60240558.42</v>
       </c>
     </row>
     <row r="43">
@@ -2406,40 +2406,40 @@
         </is>
       </c>
       <c r="C43">
-        <v>2725.077</v>
+        <v>2727.044</v>
       </c>
       <c r="D43">
-        <v>1727.62</v>
+        <v>1726.006</v>
       </c>
       <c r="E43">
-        <v>3912.255</v>
+        <v>3913.62</v>
       </c>
       <c r="F43">
-        <v>1537.151</v>
+        <v>349.512</v>
       </c>
       <c r="G43">
-        <v>949.885</v>
+        <v>216.006</v>
       </c>
       <c r="H43">
-        <v>2244.947</v>
+        <v>510.666</v>
       </c>
       <c r="I43">
-        <v>62051969.817</v>
+        <v>45915675.614</v>
       </c>
       <c r="J43">
-        <v>39419002.971</v>
+        <v>29098585.94</v>
       </c>
       <c r="K43">
-        <v>88813569.95100001</v>
+        <v>65857864.721</v>
       </c>
       <c r="L43">
-        <v>204589142.87</v>
+        <v>46487627.686</v>
       </c>
       <c r="M43">
-        <v>125752172.81</v>
+        <v>28665548.81</v>
       </c>
       <c r="N43">
-        <v>298452066.821</v>
+        <v>68030778.223</v>
       </c>
     </row>
     <row r="44">
@@ -2454,22 +2454,22 @@
         </is>
       </c>
       <c r="C44">
-        <v>15707.133</v>
+        <v>15708.655</v>
       </c>
       <c r="D44">
-        <v>9431.946</v>
+        <v>9391.478999999999</v>
       </c>
       <c r="E44">
-        <v>23116.076</v>
+        <v>23150.484</v>
       </c>
       <c r="F44">
-        <v>28414.589</v>
+        <v>28428.292</v>
       </c>
       <c r="G44">
-        <v>16776.305</v>
+        <v>16936.968</v>
       </c>
       <c r="H44">
-        <v>42158.205</v>
+        <v>42134.79</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>3776674830.576</v>
+        <v>3781969180.674</v>
       </c>
       <c r="M44">
-        <v>2238842791.855</v>
+        <v>2248513604.1</v>
       </c>
       <c r="N44">
-        <v>5609710454.872</v>
+        <v>5606316529.621</v>
       </c>
     </row>
     <row r="45">
@@ -2502,22 +2502,22 @@
         </is>
       </c>
       <c r="C45">
-        <v>35855.959</v>
+        <v>35859.163</v>
       </c>
       <c r="D45">
-        <v>22555.317</v>
+        <v>22604.22</v>
       </c>
       <c r="E45">
-        <v>51332.483</v>
+        <v>51334.498</v>
       </c>
       <c r="F45">
-        <v>57045.493</v>
+        <v>57022.372</v>
       </c>
       <c r="G45">
-        <v>35812.832</v>
+        <v>35836.885</v>
       </c>
       <c r="H45">
-        <v>82260.766</v>
+        <v>81970.068</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>7589794867.567</v>
+        <v>7587642978.428</v>
       </c>
       <c r="M45">
-        <v>4754095948.446</v>
+        <v>4763829616.074</v>
       </c>
       <c r="N45">
-        <v>10909690911.747</v>
+        <v>10912951614.14</v>
       </c>
     </row>
     <row r="46">
@@ -2550,22 +2550,22 @@
         </is>
       </c>
       <c r="C46">
-        <v>42019.752</v>
+        <v>42012.756</v>
       </c>
       <c r="D46">
-        <v>26255.69</v>
+        <v>26174.23</v>
       </c>
       <c r="E46">
-        <v>60415.728</v>
+        <v>60441.672</v>
       </c>
       <c r="F46">
-        <v>54572.009</v>
+        <v>54630.086</v>
       </c>
       <c r="G46">
-        <v>33999.455</v>
+        <v>34094.913</v>
       </c>
       <c r="H46">
-        <v>78532.996</v>
+        <v>78722.342</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7260323899.998</v>
+        <v>7262928011.096</v>
       </c>
       <c r="M46">
-        <v>4527102123.591</v>
+        <v>4533896843.822</v>
       </c>
       <c r="N46">
-        <v>10458430368.509</v>
+        <v>10480266032.26</v>
       </c>
     </row>
     <row r="47">
@@ -2598,22 +2598,22 @@
         </is>
       </c>
       <c r="C47">
-        <v>24351.732</v>
+        <v>24358.308</v>
       </c>
       <c r="D47">
-        <v>15371.782</v>
+        <v>15395.543</v>
       </c>
       <c r="E47">
-        <v>34878.914</v>
+        <v>34890.458</v>
       </c>
       <c r="F47">
-        <v>24481.651</v>
+        <v>24522.782</v>
       </c>
       <c r="G47">
-        <v>15419.828</v>
+        <v>15421.869</v>
       </c>
       <c r="H47">
-        <v>35093.868</v>
+        <v>35162.31</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>3256096545.338</v>
+        <v>3257028031.666</v>
       </c>
       <c r="M47">
-        <v>2042092050.222</v>
+        <v>2043837196.652</v>
       </c>
       <c r="N47">
-        <v>4677705890.075</v>
+        <v>4683277736.371</v>
       </c>
     </row>
     <row r="48">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="C48">
-        <v>36735.264</v>
+        <v>36696.251</v>
       </c>
       <c r="D48">
-        <v>23690.881</v>
+        <v>23741.537</v>
       </c>
       <c r="E48">
-        <v>51945.667</v>
+        <v>51851.042</v>
       </c>
       <c r="F48">
-        <v>26345.891</v>
+        <v>26340.887</v>
       </c>
       <c r="G48">
-        <v>16953.297</v>
+        <v>16936.908</v>
       </c>
       <c r="H48">
-        <v>37417.089</v>
+        <v>37416.837</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3499806520.943</v>
+        <v>3502827893.821</v>
       </c>
       <c r="M48">
-        <v>2244728828.516</v>
+        <v>2250181569.693</v>
       </c>
       <c r="N48">
-        <v>4981465813.854</v>
+        <v>4980751203.073</v>
       </c>
     </row>
     <row r="49">
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="C49">
-        <v>21807.869</v>
+        <v>21794.189</v>
       </c>
       <c r="D49">
-        <v>14111.355</v>
+        <v>14112.31</v>
       </c>
       <c r="E49">
-        <v>30869.333</v>
+        <v>30814.826</v>
       </c>
       <c r="F49">
-        <v>9600.481</v>
+        <v>9581.915999999999</v>
       </c>
       <c r="G49">
-        <v>6178.903</v>
+        <v>6160.599</v>
       </c>
       <c r="H49">
-        <v>13598.17</v>
+        <v>13601.732</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1276801067.259</v>
+        <v>1275819844.746</v>
       </c>
       <c r="M49">
-        <v>820737927.215</v>
+        <v>819037428.095</v>
       </c>
       <c r="N49">
-        <v>1807414978.077</v>
+        <v>1808044493.008</v>
       </c>
     </row>
     <row r="50">

--- a/output/Tables/2019/Resampling/HIA_per_age.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age.xlsx
@@ -434,26 +434,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C2">
-        <v>105.164</v>
+        <v>448.491</v>
       </c>
       <c r="D2">
-        <v>66.538</v>
+        <v>372.925</v>
       </c>
       <c r="E2">
-        <v>147.353</v>
+        <v>527.673</v>
       </c>
       <c r="F2">
-        <v>1044.188</v>
+        <v>4274.065</v>
       </c>
       <c r="G2">
-        <v>663.479</v>
+        <v>3556.932</v>
       </c>
       <c r="H2">
-        <v>1461.818</v>
+        <v>5024.591</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>138885904.951</v>
+        <v>568323919.3099999</v>
       </c>
       <c r="M2">
-        <v>88215796.623</v>
+        <v>472974949.987</v>
       </c>
       <c r="N2">
-        <v>194497330.904</v>
+        <v>668190075.255</v>
       </c>
     </row>
     <row r="3">
@@ -482,26 +482,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C3">
-        <v>271.651</v>
+        <v>861.742</v>
       </c>
       <c r="D3">
-        <v>179.954</v>
+        <v>726.659</v>
       </c>
       <c r="E3">
-        <v>371.353</v>
+        <v>1002.421</v>
       </c>
       <c r="F3">
-        <v>2348.245</v>
+        <v>6681.877</v>
       </c>
       <c r="G3">
-        <v>1564.782</v>
+        <v>5644.158</v>
       </c>
       <c r="H3">
-        <v>3204.92</v>
+        <v>7767.589</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>312295305.519</v>
+        <v>888997513.066</v>
       </c>
       <c r="M3">
-        <v>207941747.204</v>
+        <v>750304219.4299999</v>
       </c>
       <c r="N3">
-        <v>427239763.101</v>
+        <v>1033320642.738</v>
       </c>
     </row>
     <row r="4">
@@ -530,26 +530,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C4">
-        <v>853.915</v>
+        <v>2287.269</v>
       </c>
       <c r="D4">
-        <v>549.08</v>
+        <v>1933.988</v>
       </c>
       <c r="E4">
-        <v>1188.979</v>
+        <v>2656.641</v>
       </c>
       <c r="F4">
-        <v>5854.116</v>
+        <v>14151.994</v>
       </c>
       <c r="G4">
-        <v>3783.528</v>
+        <v>11967.93</v>
       </c>
       <c r="H4">
-        <v>8132.253</v>
+        <v>16430.584</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>779848626.149</v>
+        <v>1883184561.865</v>
       </c>
       <c r="M4">
-        <v>502433195.407</v>
+        <v>1591019391.073</v>
       </c>
       <c r="N4">
-        <v>1085196456.925</v>
+        <v>2186090301.067</v>
       </c>
     </row>
     <row r="5">
@@ -578,26 +578,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C5">
-        <v>1502.802</v>
+        <v>4887.315</v>
       </c>
       <c r="D5">
-        <v>983.9</v>
+        <v>4127.432</v>
       </c>
       <c r="E5">
-        <v>2072.692</v>
+        <v>5663.309</v>
       </c>
       <c r="F5">
-        <v>7911.05</v>
+        <v>21940.315</v>
       </c>
       <c r="G5">
-        <v>5198.274</v>
+        <v>18540.011</v>
       </c>
       <c r="H5">
-        <v>10889.464</v>
+        <v>25392.954</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1052179387.259</v>
+        <v>2917885424.216</v>
       </c>
       <c r="M5">
-        <v>690157361.177</v>
+        <v>2466906659.924</v>
       </c>
       <c r="N5">
-        <v>1447546006.962</v>
+        <v>3375720380.454</v>
       </c>
     </row>
     <row r="6">
@@ -626,26 +626,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C6">
-        <v>4650.265</v>
+        <v>10427.593</v>
       </c>
       <c r="D6">
-        <v>3201.203</v>
+        <v>8859.281000000001</v>
       </c>
       <c r="E6">
-        <v>6256.746</v>
+        <v>12025.528</v>
       </c>
       <c r="F6">
-        <v>16738.384</v>
+        <v>29710.038</v>
       </c>
       <c r="G6">
-        <v>11476.533</v>
+        <v>25235.649</v>
       </c>
       <c r="H6">
-        <v>22551.762</v>
+        <v>34197.946</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2225742311.75</v>
+        <v>3950490237.81</v>
       </c>
       <c r="M6">
-        <v>1526387292.416</v>
+        <v>3359102390.041</v>
       </c>
       <c r="N6">
-        <v>2995732197.023</v>
+        <v>4548095319.839</v>
       </c>
     </row>
     <row r="7">
@@ -674,26 +674,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C7">
-        <v>9016.529</v>
+        <v>16753.64</v>
       </c>
       <c r="D7">
-        <v>6171.962</v>
+        <v>14116.498</v>
       </c>
       <c r="E7">
-        <v>12143.782</v>
+        <v>19484.179</v>
       </c>
       <c r="F7">
-        <v>17286.886</v>
+        <v>20716.864</v>
       </c>
       <c r="G7">
-        <v>11876.006</v>
+        <v>17522.823</v>
       </c>
       <c r="H7">
-        <v>23243.947</v>
+        <v>23948.841</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2297291510.689</v>
+        <v>2754960868.613</v>
       </c>
       <c r="M7">
-        <v>1580389970.694</v>
+        <v>2328803769.141</v>
       </c>
       <c r="N7">
-        <v>3086798949.227</v>
+        <v>3185151124.847</v>
       </c>
     </row>
     <row r="8">
@@ -722,26 +722,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C8">
-        <v>20999.371</v>
+        <v>22787.649</v>
       </c>
       <c r="D8">
-        <v>14596.844</v>
+        <v>18911.896</v>
       </c>
       <c r="E8">
-        <v>28141.84</v>
+        <v>26980.957</v>
       </c>
       <c r="F8">
-        <v>6003.381</v>
+        <v>3320.724</v>
       </c>
       <c r="G8">
-        <v>4014.099</v>
+        <v>2654.717</v>
       </c>
       <c r="H8">
-        <v>8191.153</v>
+        <v>4051.753</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>798059479.1900001</v>
+        <v>441545724.466</v>
       </c>
       <c r="M8">
-        <v>533611225.902</v>
+        <v>352800943.056</v>
       </c>
       <c r="N8">
-        <v>1089336758.762</v>
+        <v>539025476.892</v>
       </c>
     </row>
     <row r="9">
@@ -770,44 +770,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C9">
-        <v>28.469</v>
+        <v>226.676</v>
       </c>
       <c r="D9">
-        <v>15.357</v>
+        <v>139.757</v>
       </c>
       <c r="E9">
-        <v>44.643</v>
+        <v>312.373</v>
       </c>
       <c r="F9">
-        <v>19.004</v>
+        <v>142.645</v>
       </c>
       <c r="G9">
-        <v>10.252</v>
+        <v>87.962</v>
       </c>
       <c r="H9">
-        <v>29.839</v>
+        <v>196.522</v>
       </c>
       <c r="I9">
-        <v>1584135.757</v>
+        <v>12624668.187</v>
       </c>
       <c r="J9">
-        <v>855202.175</v>
+        <v>7792804.372</v>
       </c>
       <c r="K9">
-        <v>2483649.79</v>
+        <v>17385898.071</v>
       </c>
       <c r="L9">
-        <v>2528315.894</v>
+        <v>18977742.602</v>
       </c>
       <c r="M9">
-        <v>1366622.1</v>
+        <v>11674435.013</v>
       </c>
       <c r="N9">
-        <v>3957706.677</v>
+        <v>26118885.61</v>
       </c>
     </row>
     <row r="10">
@@ -818,44 +818,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C10">
-        <v>73.598</v>
+        <v>481.067</v>
       </c>
       <c r="D10">
-        <v>41.068</v>
+        <v>301.971</v>
       </c>
       <c r="E10">
-        <v>111.895</v>
+        <v>659.207</v>
       </c>
       <c r="F10">
-        <v>42.689</v>
+        <v>247.822</v>
       </c>
       <c r="G10">
-        <v>23.9</v>
+        <v>155.132</v>
       </c>
       <c r="H10">
-        <v>65.137</v>
+        <v>338.704</v>
       </c>
       <c r="I10">
-        <v>4096740.045</v>
+        <v>26791010.955</v>
       </c>
       <c r="J10">
-        <v>2295002.564</v>
+        <v>16805495.931</v>
       </c>
       <c r="K10">
-        <v>6254538.618</v>
+        <v>36750028.481</v>
       </c>
       <c r="L10">
-        <v>5678414.587</v>
+        <v>32954795.795</v>
       </c>
       <c r="M10">
-        <v>3180493.923</v>
+        <v>20646419.903</v>
       </c>
       <c r="N10">
-        <v>8648060.064999999</v>
+        <v>44994860.097</v>
       </c>
     </row>
     <row r="11">
@@ -866,44 +866,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C11">
-        <v>261.02</v>
+        <v>1559.66</v>
       </c>
       <c r="D11">
-        <v>142.031</v>
+        <v>969.4930000000001</v>
       </c>
       <c r="E11">
-        <v>407.777</v>
+        <v>2142.644</v>
       </c>
       <c r="F11">
-        <v>119.298</v>
+        <v>641.8200000000001</v>
       </c>
       <c r="G11">
-        <v>65.172</v>
+        <v>399.698</v>
       </c>
       <c r="H11">
-        <v>185.628</v>
+        <v>882.259</v>
       </c>
       <c r="I11">
-        <v>14539791.89</v>
+        <v>86862575.758</v>
       </c>
       <c r="J11">
-        <v>7897547.72</v>
+        <v>53974077.022</v>
       </c>
       <c r="K11">
-        <v>22732268.484</v>
+        <v>119437917.617</v>
       </c>
       <c r="L11">
-        <v>15852215.657</v>
+        <v>85328318.935</v>
       </c>
       <c r="M11">
-        <v>8672479.662</v>
+        <v>53111722.416</v>
       </c>
       <c r="N11">
-        <v>24673858.743</v>
+        <v>117228310.514</v>
       </c>
     </row>
     <row r="12">
@@ -914,44 +914,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C12">
-        <v>574.349</v>
+        <v>3899.596</v>
       </c>
       <c r="D12">
-        <v>317.794</v>
+        <v>2432.391</v>
       </c>
       <c r="E12">
-        <v>884.431</v>
+        <v>5322.98</v>
       </c>
       <c r="F12">
-        <v>199.533</v>
+        <v>1154.881</v>
       </c>
       <c r="G12">
-        <v>110.762</v>
+        <v>719.85</v>
       </c>
       <c r="H12">
-        <v>307.445</v>
+        <v>1577.98</v>
       </c>
       <c r="I12">
-        <v>32004100.982</v>
+        <v>217175593.428</v>
       </c>
       <c r="J12">
-        <v>17745373.766</v>
+        <v>135546755.519</v>
       </c>
       <c r="K12">
-        <v>49235496.246</v>
+        <v>296551668.02</v>
       </c>
       <c r="L12">
-        <v>26527836.692</v>
+        <v>153570403.495</v>
       </c>
       <c r="M12">
-        <v>14730922.656</v>
+        <v>95723178.389</v>
       </c>
       <c r="N12">
-        <v>40811298.333</v>
+        <v>209678945.791</v>
       </c>
     </row>
     <row r="13">
@@ -962,44 +962,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C13">
-        <v>2142.897</v>
+        <v>11159.917</v>
       </c>
       <c r="D13">
-        <v>1250.567</v>
+        <v>7133.372</v>
       </c>
       <c r="E13">
-        <v>3201.941</v>
+        <v>15019.866</v>
       </c>
       <c r="F13">
-        <v>512.673</v>
+        <v>2145.669</v>
       </c>
       <c r="G13">
-        <v>297.551</v>
+        <v>1367.447</v>
       </c>
       <c r="H13">
-        <v>766.425</v>
+        <v>2887.826</v>
       </c>
       <c r="I13">
-        <v>119466879.706</v>
+        <v>621559543.668</v>
       </c>
       <c r="J13">
-        <v>69897724.64</v>
+        <v>397801316.344</v>
       </c>
       <c r="K13">
-        <v>178113982.548</v>
+        <v>836743352.5829999</v>
       </c>
       <c r="L13">
-        <v>68222100.41500001</v>
+        <v>285356608.735</v>
       </c>
       <c r="M13">
-        <v>39662525.4</v>
+        <v>181946455.915</v>
       </c>
       <c r="N13">
-        <v>101995498.273</v>
+        <v>384012357.243</v>
       </c>
     </row>
     <row r="14">
@@ -1010,44 +1010,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C14">
-        <v>3627.998</v>
+        <v>13342.465</v>
       </c>
       <c r="D14">
-        <v>2105.416</v>
+        <v>8367.494000000001</v>
       </c>
       <c r="E14">
-        <v>5412.612</v>
+        <v>18155.831</v>
       </c>
       <c r="F14">
-        <v>498.561</v>
+        <v>1265.924</v>
       </c>
       <c r="G14">
-        <v>289.661</v>
+        <v>788.644</v>
       </c>
       <c r="H14">
-        <v>743.985</v>
+        <v>1728.698</v>
       </c>
       <c r="I14">
-        <v>202017014.366</v>
+        <v>743024097.918</v>
       </c>
       <c r="J14">
-        <v>117144422.931</v>
+        <v>466513932.484</v>
       </c>
       <c r="K14">
-        <v>301981847.832</v>
+        <v>1012396149.154</v>
       </c>
       <c r="L14">
-        <v>66270202.803</v>
+        <v>168339263.48</v>
       </c>
       <c r="M14">
-        <v>38460212.152</v>
+        <v>104968881.445</v>
       </c>
       <c r="N14">
-        <v>99110109.619</v>
+        <v>229648465.201</v>
       </c>
     </row>
     <row r="15">
@@ -1058,44 +1058,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C15">
-        <v>3657.188</v>
+        <v>8708.471</v>
       </c>
       <c r="D15">
-        <v>2060.469</v>
+        <v>5378.961</v>
       </c>
       <c r="E15">
-        <v>5574.494</v>
+        <v>12113.072</v>
       </c>
       <c r="F15">
-        <v>121.132</v>
+        <v>122.629</v>
       </c>
       <c r="G15">
-        <v>65.474</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="H15">
-        <v>188.479</v>
+        <v>176.202</v>
       </c>
       <c r="I15">
-        <v>203886102.25</v>
+        <v>485254186.821</v>
       </c>
       <c r="J15">
-        <v>115016573.579</v>
+        <v>300097445.338</v>
       </c>
       <c r="K15">
-        <v>309687708.965</v>
+        <v>674286819.957</v>
       </c>
       <c r="L15">
-        <v>16096085.861</v>
+        <v>16294216.201</v>
       </c>
       <c r="M15">
-        <v>8729641.296</v>
+        <v>9649085.187000001</v>
       </c>
       <c r="N15">
-        <v>25031031.94</v>
+        <v>23420968.231</v>
       </c>
     </row>
     <row r="16">
@@ -1106,44 +1106,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C16">
-        <v>0.467</v>
+        <v>6.528</v>
       </c>
       <c r="D16">
-        <v>0.011</v>
+        <v>0.166</v>
       </c>
       <c r="E16">
-        <v>1.055</v>
+        <v>13.247</v>
       </c>
       <c r="F16">
-        <v>0.348</v>
+        <v>4.534</v>
       </c>
       <c r="G16">
-        <v>0.008</v>
+        <v>0.116</v>
       </c>
       <c r="H16">
-        <v>0.79</v>
+        <v>9.247999999999999</v>
       </c>
       <c r="I16">
-        <v>20554.571</v>
+        <v>287831.257</v>
       </c>
       <c r="J16">
-        <v>468.362</v>
+        <v>7277.481</v>
       </c>
       <c r="K16">
-        <v>46467.716</v>
+        <v>583349.034</v>
       </c>
       <c r="L16">
-        <v>46203.284</v>
+        <v>603332.035</v>
       </c>
       <c r="M16">
-        <v>1030.941</v>
+        <v>15268.137</v>
       </c>
       <c r="N16">
-        <v>104742.375</v>
+        <v>1226370.443</v>
       </c>
     </row>
     <row r="17">
@@ -1154,44 +1154,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C17">
-        <v>14.474</v>
+        <v>60.959</v>
       </c>
       <c r="D17">
-        <v>0.229</v>
+        <v>1.479</v>
       </c>
       <c r="E17">
-        <v>31.812</v>
+        <v>121.819</v>
       </c>
       <c r="F17">
-        <v>9.462</v>
+        <v>35.977</v>
       </c>
       <c r="G17">
-        <v>0.148</v>
+        <v>0.874</v>
       </c>
       <c r="H17">
-        <v>20.899</v>
+        <v>72.148</v>
       </c>
       <c r="I17">
-        <v>638004.071</v>
+        <v>2684399.428</v>
       </c>
       <c r="J17">
-        <v>10110.254</v>
+        <v>65194.105</v>
       </c>
       <c r="K17">
-        <v>1406073.333</v>
+        <v>5374154.762</v>
       </c>
       <c r="L17">
-        <v>1259859.543</v>
+        <v>4790454.453</v>
       </c>
       <c r="M17">
-        <v>19879.603</v>
+        <v>116207.783</v>
       </c>
       <c r="N17">
-        <v>2780429.242</v>
+        <v>9608915.275</v>
       </c>
     </row>
     <row r="18">
@@ -1202,44 +1202,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C18">
-        <v>70.262</v>
+        <v>166.366</v>
       </c>
       <c r="D18">
-        <v>1.373</v>
+        <v>4.607</v>
       </c>
       <c r="E18">
-        <v>152.098</v>
+        <v>330.471</v>
       </c>
       <c r="F18">
-        <v>38.102</v>
+        <v>81.111</v>
       </c>
       <c r="G18">
-        <v>0.734</v>
+        <v>2.223</v>
       </c>
       <c r="H18">
-        <v>82.557</v>
+        <v>161.129</v>
       </c>
       <c r="I18">
-        <v>3099113.282</v>
+        <v>7336283.522</v>
       </c>
       <c r="J18">
-        <v>61124.972</v>
+        <v>204331.269</v>
       </c>
       <c r="K18">
-        <v>6706167.37</v>
+        <v>14577786.057</v>
       </c>
       <c r="L18">
-        <v>5075938.066</v>
+        <v>10788509.07</v>
       </c>
       <c r="M18">
-        <v>98145.505</v>
+        <v>297297.215</v>
       </c>
       <c r="N18">
-        <v>11021792.44</v>
+        <v>21485336.77</v>
       </c>
     </row>
     <row r="19">
@@ -1250,44 +1250,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C19">
-        <v>98.146</v>
+        <v>253.651</v>
       </c>
       <c r="D19">
-        <v>2.096</v>
+        <v>6.417</v>
       </c>
       <c r="E19">
-        <v>212.406</v>
+        <v>502.503</v>
       </c>
       <c r="F19">
-        <v>41.382</v>
+        <v>91.673</v>
       </c>
       <c r="G19">
-        <v>0.891</v>
+        <v>2.338</v>
       </c>
       <c r="H19">
-        <v>90.002</v>
+        <v>181.907</v>
       </c>
       <c r="I19">
-        <v>4325248.872</v>
+        <v>11170708.678</v>
       </c>
       <c r="J19">
-        <v>91478.804</v>
+        <v>284993.289</v>
       </c>
       <c r="K19">
-        <v>9383529.988</v>
+        <v>22174509.11</v>
       </c>
       <c r="L19">
-        <v>5500152.964</v>
+        <v>12192208.892</v>
       </c>
       <c r="M19">
-        <v>119086.77</v>
+        <v>312048.219</v>
       </c>
       <c r="N19">
-        <v>11936714.201</v>
+        <v>24148334.836</v>
       </c>
     </row>
     <row r="20">
@@ -1298,44 +1298,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C20">
-        <v>197.027</v>
+        <v>369.148</v>
       </c>
       <c r="D20">
-        <v>3.166</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E20">
-        <v>426.477</v>
+        <v>730.418</v>
       </c>
       <c r="F20">
-        <v>59.967</v>
+        <v>93.142</v>
       </c>
       <c r="G20">
-        <v>0.966</v>
+        <v>2.03</v>
       </c>
       <c r="H20">
-        <v>129.788</v>
+        <v>184.113</v>
       </c>
       <c r="I20">
-        <v>8696722.370999999</v>
+        <v>16292320.395</v>
       </c>
       <c r="J20">
-        <v>138699.496</v>
+        <v>359569.578</v>
       </c>
       <c r="K20">
-        <v>18748487.971</v>
+        <v>32204944.651</v>
       </c>
       <c r="L20">
-        <v>7968511.67</v>
+        <v>12378308.871</v>
       </c>
       <c r="M20">
-        <v>130499.029</v>
+        <v>270008.566</v>
       </c>
       <c r="N20">
-        <v>17282947.045</v>
+        <v>24515074.352</v>
       </c>
     </row>
     <row r="21">
@@ -1346,44 +1346,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C21">
-        <v>247.096</v>
+        <v>274.784</v>
       </c>
       <c r="D21">
-        <v>4.133</v>
+        <v>7.11</v>
       </c>
       <c r="E21">
-        <v>533.022</v>
+        <v>543.36</v>
       </c>
       <c r="F21">
-        <v>47.337</v>
+        <v>39.948</v>
       </c>
       <c r="G21">
-        <v>0.803</v>
+        <v>0.988</v>
       </c>
       <c r="H21">
-        <v>101.906</v>
+        <v>79.185</v>
       </c>
       <c r="I21">
-        <v>10899948.904</v>
+        <v>12127656.813</v>
       </c>
       <c r="J21">
-        <v>180464.276</v>
+        <v>312238.422</v>
       </c>
       <c r="K21">
-        <v>23516330.138</v>
+        <v>23906849.607</v>
       </c>
       <c r="L21">
-        <v>6297546.723</v>
+        <v>5319096.246</v>
       </c>
       <c r="M21">
-        <v>105239.249</v>
+        <v>131065.823</v>
       </c>
       <c r="N21">
-        <v>13564934.711</v>
+        <v>10538861.263</v>
       </c>
     </row>
     <row r="22">
@@ -1394,44 +1394,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C22">
-        <v>137.084</v>
+        <v>124.355</v>
       </c>
       <c r="D22">
-        <v>3.642</v>
+        <v>4.074</v>
       </c>
       <c r="E22">
-        <v>290.899</v>
+        <v>247.321</v>
       </c>
       <c r="F22">
-        <v>8.074</v>
+        <v>3.616</v>
       </c>
       <c r="G22">
-        <v>0.199</v>
+        <v>0.113</v>
       </c>
       <c r="H22">
-        <v>17.399</v>
+        <v>7.317</v>
       </c>
       <c r="I22">
-        <v>6045192.293</v>
+        <v>5481398.38</v>
       </c>
       <c r="J22">
-        <v>161319.524</v>
+        <v>180272.451</v>
       </c>
       <c r="K22">
-        <v>12811626.869</v>
+        <v>10913752.311</v>
       </c>
       <c r="L22">
-        <v>1074188.379</v>
+        <v>480983.852</v>
       </c>
       <c r="M22">
-        <v>26214.597</v>
+        <v>15086.521</v>
       </c>
       <c r="N22">
-        <v>2315381.838</v>
+        <v>974218.181</v>
       </c>
     </row>
     <row r="23">
@@ -1442,44 +1442,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C23">
-        <v>12.27</v>
+        <v>1893.606</v>
       </c>
       <c r="D23">
-        <v>0.281</v>
+        <v>51.513</v>
       </c>
       <c r="E23">
-        <v>26.964</v>
+        <v>3757.498</v>
       </c>
       <c r="F23">
-        <v>7.053</v>
+        <v>1058.77</v>
       </c>
       <c r="G23">
-        <v>0.161</v>
+        <v>29.067</v>
       </c>
       <c r="H23">
-        <v>15.523</v>
+        <v>2101.267</v>
       </c>
       <c r="I23">
-        <v>181853.462</v>
+        <v>28035782.581</v>
       </c>
       <c r="J23">
-        <v>4168.398</v>
+        <v>760395.046</v>
       </c>
       <c r="K23">
-        <v>398959.379</v>
+        <v>55477424.976</v>
       </c>
       <c r="L23">
-        <v>938778.714</v>
+        <v>140823281.175</v>
       </c>
       <c r="M23">
-        <v>21243.003</v>
+        <v>3798594.882</v>
       </c>
       <c r="N23">
-        <v>2069038.434</v>
+        <v>279883284.782</v>
       </c>
     </row>
     <row r="24">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C24">
-        <v>75.983</v>
+        <v>3253.802</v>
       </c>
       <c r="D24">
-        <v>1.241</v>
+        <v>81.538</v>
       </c>
       <c r="E24">
-        <v>163.473</v>
+        <v>6454.539</v>
       </c>
       <c r="F24">
-        <v>38.558</v>
+        <v>1526.314</v>
       </c>
       <c r="G24">
-        <v>0.627</v>
+        <v>38.168</v>
       </c>
       <c r="H24">
-        <v>82.836</v>
+        <v>3023.812</v>
       </c>
       <c r="I24">
-        <v>1123468.99</v>
+        <v>48159696.811</v>
       </c>
       <c r="J24">
-        <v>18377.971</v>
+        <v>1215253.56</v>
       </c>
       <c r="K24">
-        <v>2419882.012</v>
+        <v>95551590.322</v>
       </c>
       <c r="L24">
-        <v>5126630.194</v>
+        <v>202857513.568</v>
       </c>
       <c r="M24">
-        <v>83733.766</v>
+        <v>5035584.071</v>
       </c>
       <c r="N24">
-        <v>11055361.778</v>
+        <v>402948266.95</v>
       </c>
     </row>
     <row r="25">
@@ -1538,44 +1538,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C25">
-        <v>244.783</v>
+        <v>4227.728</v>
       </c>
       <c r="D25">
-        <v>4.819</v>
+        <v>120.298</v>
       </c>
       <c r="E25">
-        <v>532.879</v>
+        <v>8355.91</v>
       </c>
       <c r="F25">
-        <v>100.099</v>
+        <v>1601.907</v>
       </c>
       <c r="G25">
-        <v>1.967</v>
+        <v>45.054</v>
       </c>
       <c r="H25">
-        <v>217.486</v>
+        <v>3169.984</v>
       </c>
       <c r="I25">
-        <v>3625475.743</v>
+        <v>62609464.61</v>
       </c>
       <c r="J25">
-        <v>70834.727</v>
+        <v>1778342.734</v>
       </c>
       <c r="K25">
-        <v>7878520.857</v>
+        <v>123778116.781</v>
       </c>
       <c r="L25">
-        <v>13298365.372</v>
+        <v>212766369.544</v>
       </c>
       <c r="M25">
-        <v>260240.805</v>
+        <v>5958834.509</v>
       </c>
       <c r="N25">
-        <v>28959434.772</v>
+        <v>421613253.085</v>
       </c>
     </row>
     <row r="26">
@@ -1586,44 +1586,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C26">
-        <v>404.553</v>
+        <v>5657.545</v>
       </c>
       <c r="D26">
-        <v>8.571</v>
+        <v>145.697</v>
       </c>
       <c r="E26">
-        <v>869.501</v>
+        <v>11145.373</v>
       </c>
       <c r="F26">
-        <v>124.441</v>
+        <v>1537.868</v>
       </c>
       <c r="G26">
-        <v>2.632</v>
+        <v>39.705</v>
       </c>
       <c r="H26">
-        <v>268.455</v>
+        <v>3030.738</v>
       </c>
       <c r="I26">
-        <v>5975195.907</v>
+        <v>83730258.132</v>
       </c>
       <c r="J26">
-        <v>127210.737</v>
+        <v>2155523.109</v>
       </c>
       <c r="K26">
-        <v>12872608.872</v>
+        <v>165003196.556</v>
       </c>
       <c r="L26">
-        <v>16560898.807</v>
+        <v>204402592.641</v>
       </c>
       <c r="M26">
-        <v>358261.704</v>
+        <v>5272398.716</v>
       </c>
       <c r="N26">
-        <v>35599321.398</v>
+        <v>403342662.181</v>
       </c>
     </row>
     <row r="27">
@@ -1634,44 +1634,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C27">
-        <v>1415.376</v>
+        <v>8151.597</v>
       </c>
       <c r="D27">
-        <v>19.559</v>
+        <v>174.203</v>
       </c>
       <c r="E27">
-        <v>3018.289</v>
+        <v>16073.025</v>
       </c>
       <c r="F27">
-        <v>292.816</v>
+        <v>1443.589</v>
       </c>
       <c r="G27">
-        <v>4.13</v>
+        <v>31.053</v>
       </c>
       <c r="H27">
-        <v>625.5069999999999</v>
+        <v>2853.306</v>
       </c>
       <c r="I27">
-        <v>20982325.568</v>
+        <v>120745802.531</v>
       </c>
       <c r="J27">
-        <v>288163.25</v>
+        <v>2578842.798</v>
       </c>
       <c r="K27">
-        <v>44589518.674</v>
+        <v>238044167.037</v>
       </c>
       <c r="L27">
-        <v>38939637.511</v>
+        <v>192127118.108</v>
       </c>
       <c r="M27">
-        <v>548370.599</v>
+        <v>4128126.927</v>
       </c>
       <c r="N27">
-        <v>82953429.11499999</v>
+        <v>379903751.165</v>
       </c>
     </row>
     <row r="28">
@@ -1682,44 +1682,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C28">
-        <v>1548.372</v>
+        <v>5404.212</v>
       </c>
       <c r="D28">
-        <v>24.279</v>
+        <v>135.927</v>
       </c>
       <c r="E28">
-        <v>3271.512</v>
+        <v>10630.46</v>
       </c>
       <c r="F28">
-        <v>187.558</v>
+        <v>456.439</v>
       </c>
       <c r="G28">
-        <v>2.965</v>
+        <v>11.311</v>
       </c>
       <c r="H28">
-        <v>397.039</v>
+        <v>898.789</v>
       </c>
       <c r="I28">
-        <v>22870939.064</v>
+        <v>80011681.31200001</v>
       </c>
       <c r="J28">
-        <v>354637.753</v>
+        <v>2009896.933</v>
       </c>
       <c r="K28">
-        <v>48486117.682</v>
+        <v>157493290.229</v>
       </c>
       <c r="L28">
-        <v>24919803.941</v>
+        <v>60687650.993</v>
       </c>
       <c r="M28">
-        <v>399107.922</v>
+        <v>1506109.587</v>
       </c>
       <c r="N28">
-        <v>52732601.913</v>
+        <v>119631520.449</v>
       </c>
     </row>
     <row r="29">
@@ -1730,44 +1730,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C29">
-        <v>1110.284</v>
+        <v>2147.808</v>
       </c>
       <c r="D29">
-        <v>27.785</v>
+        <v>67.083</v>
       </c>
       <c r="E29">
-        <v>2349.741</v>
+        <v>4271.429</v>
       </c>
       <c r="F29">
-        <v>32.238</v>
+        <v>24.501</v>
       </c>
       <c r="G29">
-        <v>0.797</v>
+        <v>0.771</v>
       </c>
       <c r="H29">
-        <v>69.73</v>
+        <v>49.678</v>
       </c>
       <c r="I29">
-        <v>16450196.852</v>
+        <v>31810009.392</v>
       </c>
       <c r="J29">
-        <v>411318.542</v>
+        <v>995211.5919999999</v>
       </c>
       <c r="K29">
-        <v>34847807.536</v>
+        <v>63210546.572</v>
       </c>
       <c r="L29">
-        <v>4281199.096</v>
+        <v>3256849.302</v>
       </c>
       <c r="M29">
-        <v>103702.421</v>
+        <v>100910.075</v>
       </c>
       <c r="N29">
-        <v>9242259.648</v>
+        <v>6579510.53</v>
       </c>
     </row>
     <row r="30">
@@ -1778,44 +1778,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C30">
-        <v>43.948</v>
+        <v>399.407</v>
       </c>
       <c r="D30">
-        <v>-0.011</v>
+        <v>1.457</v>
       </c>
       <c r="E30">
-        <v>91.819</v>
+        <v>757.808</v>
       </c>
       <c r="F30">
-        <v>31.254</v>
+        <v>268.166</v>
       </c>
       <c r="G30">
-        <v>-0.017</v>
+        <v>1.065</v>
       </c>
       <c r="H30">
-        <v>65.389</v>
+        <v>507.387</v>
       </c>
       <c r="I30">
-        <v>3306237.049</v>
+        <v>30062019.509</v>
       </c>
       <c r="J30">
-        <v>-468.988</v>
+        <v>103798.479</v>
       </c>
       <c r="K30">
-        <v>6897293.319</v>
+        <v>56994575.396</v>
       </c>
       <c r="L30">
-        <v>4152064.752</v>
+        <v>35644159.674</v>
       </c>
       <c r="M30">
-        <v>-958.372</v>
+        <v>131637.483</v>
       </c>
       <c r="N30">
-        <v>8700105.348999999</v>
+        <v>67555539.222</v>
       </c>
     </row>
     <row r="31">
@@ -1826,44 +1826,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C31">
-        <v>138.433</v>
+        <v>649.215</v>
       </c>
       <c r="D31">
-        <v>1.74</v>
+        <v>-0.377</v>
       </c>
       <c r="E31">
-        <v>281.176</v>
+        <v>1231.07</v>
       </c>
       <c r="F31">
-        <v>86.25</v>
+        <v>357.955</v>
       </c>
       <c r="G31">
-        <v>1.084</v>
+        <v>-0.214</v>
       </c>
       <c r="H31">
-        <v>175.668</v>
+        <v>676.266</v>
       </c>
       <c r="I31">
-        <v>10419315.711</v>
+        <v>48849817.705</v>
       </c>
       <c r="J31">
-        <v>125724.873</v>
+        <v>-42707.906</v>
       </c>
       <c r="K31">
-        <v>21140888.573</v>
+        <v>92447549.846</v>
       </c>
       <c r="L31">
-        <v>11499763.91</v>
+        <v>47590943.91</v>
       </c>
       <c r="M31">
-        <v>147416.079</v>
+        <v>-23157.682</v>
       </c>
       <c r="N31">
-        <v>23358217.529</v>
+        <v>90013995.711</v>
       </c>
     </row>
     <row r="32">
@@ -1874,44 +1874,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C32">
-        <v>411.126</v>
+        <v>947.6559999999999</v>
       </c>
       <c r="D32">
-        <v>0.073</v>
+        <v>1.237</v>
       </c>
       <c r="E32">
-        <v>847.063</v>
+        <v>1800.993</v>
       </c>
       <c r="F32">
-        <v>204.434</v>
+        <v>417.229</v>
       </c>
       <c r="G32">
-        <v>0.01</v>
+        <v>0.359</v>
       </c>
       <c r="H32">
-        <v>420.265</v>
+        <v>792.061</v>
       </c>
       <c r="I32">
-        <v>30951486.301</v>
+        <v>71270875.506</v>
       </c>
       <c r="J32">
-        <v>7479.263</v>
+        <v>80298.06200000001</v>
       </c>
       <c r="K32">
-        <v>63716433.726</v>
+        <v>135527906.052</v>
       </c>
       <c r="L32">
-        <v>27204734.762</v>
+        <v>55432896.002</v>
       </c>
       <c r="M32">
-        <v>-3873.371</v>
+        <v>55668.372</v>
       </c>
       <c r="N32">
-        <v>55881699.374</v>
+        <v>105298072.637</v>
       </c>
     </row>
     <row r="33">
@@ -1922,44 +1922,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C33">
-        <v>651.325</v>
+        <v>1558.278</v>
       </c>
       <c r="D33">
-        <v>0.487</v>
+        <v>0.03</v>
       </c>
       <c r="E33">
-        <v>1328.806</v>
+        <v>2934.976</v>
       </c>
       <c r="F33">
-        <v>247.261</v>
+        <v>495.826</v>
       </c>
       <c r="G33">
-        <v>0.182</v>
+        <v>0.249</v>
       </c>
       <c r="H33">
-        <v>505.606</v>
+        <v>934.796</v>
       </c>
       <c r="I33">
-        <v>48865244.887</v>
+        <v>117078479.506</v>
       </c>
       <c r="J33">
-        <v>40187.269</v>
+        <v>-10491.586</v>
       </c>
       <c r="K33">
-        <v>99842747.042</v>
+        <v>220509631.404</v>
       </c>
       <c r="L33">
-        <v>32889067.499</v>
+        <v>65894562.362</v>
       </c>
       <c r="M33">
-        <v>36394.187</v>
+        <v>44245.237</v>
       </c>
       <c r="N33">
-        <v>67263168.536</v>
+        <v>124162396.011</v>
       </c>
     </row>
     <row r="34">
@@ -1970,44 +1970,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C34">
-        <v>2099.537</v>
+        <v>2204.605</v>
       </c>
       <c r="D34">
-        <v>-6.599</v>
+        <v>-5.532</v>
       </c>
       <c r="E34">
-        <v>4152.235</v>
+        <v>4094.745</v>
       </c>
       <c r="F34">
-        <v>552.61</v>
+        <v>479.357</v>
       </c>
       <c r="G34">
-        <v>-1.061</v>
+        <v>-0.756</v>
       </c>
       <c r="H34">
-        <v>1096.675</v>
+        <v>893.89</v>
       </c>
       <c r="I34">
-        <v>157857339.75</v>
+        <v>165815067.825</v>
       </c>
       <c r="J34">
-        <v>-527619.5159999999</v>
+        <v>-444855.056</v>
       </c>
       <c r="K34">
-        <v>311766061.526</v>
+        <v>307122763.708</v>
       </c>
       <c r="L34">
-        <v>73466457.40700001</v>
+        <v>63771708.795</v>
       </c>
       <c r="M34">
-        <v>-166481.042</v>
+        <v>-109218.477</v>
       </c>
       <c r="N34">
-        <v>145663723.143</v>
+        <v>118720647.762</v>
       </c>
     </row>
     <row r="35">
@@ -2018,44 +2018,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C35">
-        <v>2130.866</v>
+        <v>701.659</v>
       </c>
       <c r="D35">
-        <v>5.725</v>
+        <v>1.575</v>
       </c>
       <c r="E35">
-        <v>4214.574</v>
+        <v>1317.802</v>
       </c>
       <c r="F35">
-        <v>326.908</v>
+        <v>84.997</v>
       </c>
       <c r="G35">
-        <v>0.303</v>
+        <v>0.237</v>
       </c>
       <c r="H35">
-        <v>646.5410000000001</v>
+        <v>160.047</v>
       </c>
       <c r="I35">
-        <v>160307266.963</v>
+        <v>52780173.004</v>
       </c>
       <c r="J35">
-        <v>446478.101</v>
+        <v>133948.394</v>
       </c>
       <c r="K35">
-        <v>317492547.894</v>
+        <v>99192685.17</v>
       </c>
       <c r="L35">
-        <v>43485181.057</v>
+        <v>11302452.335</v>
       </c>
       <c r="M35">
-        <v>42865.557</v>
+        <v>33548.081</v>
       </c>
       <c r="N35">
-        <v>86227244.266</v>
+        <v>21296515.893</v>
       </c>
     </row>
     <row r="36">
@@ -2066,44 +2066,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C36">
-        <v>870.907</v>
+        <v>28.579</v>
       </c>
       <c r="D36">
-        <v>-1.693</v>
+        <v>-0.062</v>
       </c>
       <c r="E36">
-        <v>1767.203</v>
+        <v>54.914</v>
       </c>
       <c r="F36">
-        <v>30.646</v>
+        <v>0.622</v>
       </c>
       <c r="G36">
-        <v>0.221</v>
+        <v>0.004</v>
       </c>
       <c r="H36">
-        <v>63.559</v>
+        <v>1.228</v>
       </c>
       <c r="I36">
-        <v>65416853.911</v>
+        <v>2149369.664</v>
       </c>
       <c r="J36">
-        <v>-75352.402</v>
+        <v>-3488.04</v>
       </c>
       <c r="K36">
-        <v>132774554.068</v>
+        <v>4121347.329</v>
       </c>
       <c r="L36">
-        <v>4066275.991</v>
+        <v>82597.439</v>
       </c>
       <c r="M36">
-        <v>29072.107</v>
+        <v>469.324</v>
       </c>
       <c r="N36">
-        <v>8466495.277000001</v>
+        <v>163299.989</v>
       </c>
     </row>
     <row r="37">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C37">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C38">
@@ -2210,44 +2210,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C39">
-        <v>2.588</v>
+        <v>141.923</v>
       </c>
       <c r="D39">
-        <v>1.544</v>
+        <v>103.344</v>
       </c>
       <c r="E39">
-        <v>3.831</v>
+        <v>179.963</v>
       </c>
       <c r="F39">
-        <v>3.699</v>
+        <v>186.8</v>
       </c>
       <c r="G39">
-        <v>2.222</v>
+        <v>136.016</v>
       </c>
       <c r="H39">
-        <v>5.466</v>
+        <v>236.889</v>
       </c>
       <c r="I39">
-        <v>43504.974</v>
+        <v>2387158.058</v>
       </c>
       <c r="J39">
-        <v>26054.459</v>
+        <v>1739787.77</v>
       </c>
       <c r="K39">
-        <v>64522.588</v>
+        <v>3030234.512</v>
       </c>
       <c r="L39">
-        <v>492016.096</v>
+        <v>24827215.072</v>
       </c>
       <c r="M39">
-        <v>296198.73</v>
+        <v>18121586.298</v>
       </c>
       <c r="N39">
-        <v>728432.848</v>
+        <v>31528160.226</v>
       </c>
     </row>
     <row r="40">
@@ -2258,44 +2258,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C40">
-        <v>13.297</v>
+        <v>314.967</v>
       </c>
       <c r="D40">
-        <v>8.263999999999999</v>
+        <v>229.534</v>
       </c>
       <c r="E40">
-        <v>19.311</v>
+        <v>399.041</v>
       </c>
       <c r="F40">
-        <v>15.202</v>
+        <v>308.852</v>
       </c>
       <c r="G40">
-        <v>9.433</v>
+        <v>224.868</v>
       </c>
       <c r="H40">
-        <v>22.024</v>
+        <v>391.636</v>
       </c>
       <c r="I40">
-        <v>224171.346</v>
+        <v>5305909.929</v>
       </c>
       <c r="J40">
-        <v>139132.384</v>
+        <v>3862149.184</v>
       </c>
       <c r="K40">
-        <v>324876.072</v>
+        <v>6716388.387</v>
       </c>
       <c r="L40">
-        <v>2022764.903</v>
+        <v>41087178.267</v>
       </c>
       <c r="M40">
-        <v>1255208.248</v>
+        <v>29897306.515</v>
       </c>
       <c r="N40">
-        <v>2927264.371</v>
+        <v>52044326.903</v>
       </c>
     </row>
     <row r="41">
@@ -2306,44 +2306,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C41">
-        <v>125.745</v>
+        <v>1748.749</v>
       </c>
       <c r="D41">
-        <v>79.995</v>
+        <v>1280.507</v>
       </c>
       <c r="E41">
-        <v>179.81</v>
+        <v>2201.649</v>
       </c>
       <c r="F41">
-        <v>100.653</v>
+        <v>1080.265</v>
       </c>
       <c r="G41">
-        <v>63.626</v>
+        <v>790.23</v>
       </c>
       <c r="H41">
-        <v>144.263</v>
+        <v>1359.475</v>
       </c>
       <c r="I41">
-        <v>2115307.958</v>
+        <v>29442742.558</v>
       </c>
       <c r="J41">
-        <v>1348892.35</v>
+        <v>21593775.549</v>
       </c>
       <c r="K41">
-        <v>3025307.241</v>
+        <v>37062127.814</v>
       </c>
       <c r="L41">
-        <v>13386754.572</v>
+        <v>143676136.46</v>
       </c>
       <c r="M41">
-        <v>8490272.562000001</v>
+        <v>105221327.299</v>
       </c>
       <c r="N41">
-        <v>19167130.344</v>
+        <v>180810083.632</v>
       </c>
     </row>
     <row r="42">
@@ -2354,44 +2354,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C42">
-        <v>660.67</v>
+        <v>5032.179</v>
       </c>
       <c r="D42">
-        <v>421.229</v>
+        <v>3661.669</v>
       </c>
       <c r="E42">
-        <v>946.112</v>
+        <v>6366.488</v>
       </c>
       <c r="F42">
-        <v>316.384</v>
+        <v>1551.952</v>
       </c>
       <c r="G42">
-        <v>200.792</v>
+        <v>1128.399</v>
       </c>
       <c r="H42">
-        <v>452.846</v>
+        <v>1968.797</v>
       </c>
       <c r="I42">
-        <v>11120594.504</v>
+        <v>84709983.742</v>
       </c>
       <c r="J42">
-        <v>7068213.657</v>
+        <v>61599699.981</v>
       </c>
       <c r="K42">
-        <v>15917096.396</v>
+        <v>107246781.159</v>
       </c>
       <c r="L42">
-        <v>42035060.187</v>
+        <v>206376456.683</v>
       </c>
       <c r="M42">
-        <v>26711276.33</v>
+        <v>149893138.985</v>
       </c>
       <c r="N42">
-        <v>60240558.42</v>
+        <v>261862703.677</v>
       </c>
     </row>
     <row r="43">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C43">
-        <v>2727.044</v>
+        <v>6168.568</v>
       </c>
       <c r="D43">
-        <v>1726.006</v>
+        <v>4434.475</v>
       </c>
       <c r="E43">
-        <v>3913.62</v>
+        <v>7938.561</v>
       </c>
       <c r="F43">
-        <v>349.512</v>
+        <v>305.366</v>
       </c>
       <c r="G43">
-        <v>216.006</v>
+        <v>213.528</v>
       </c>
       <c r="H43">
-        <v>510.666</v>
+        <v>406.978</v>
       </c>
       <c r="I43">
-        <v>45915675.614</v>
+        <v>103863024.868</v>
       </c>
       <c r="J43">
-        <v>29098585.94</v>
+        <v>74749373.568</v>
       </c>
       <c r="K43">
-        <v>65857864.721</v>
+        <v>133572105.085</v>
       </c>
       <c r="L43">
-        <v>46487627.686</v>
+        <v>40604289.545</v>
       </c>
       <c r="M43">
-        <v>28665548.81</v>
+        <v>28405804.11</v>
       </c>
       <c r="N43">
-        <v>68030778.223</v>
+        <v>54236900.958</v>
       </c>
     </row>
     <row r="44">
@@ -2450,26 +2450,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20-24</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C44">
-        <v>15708.655</v>
+        <v>23393.237</v>
       </c>
       <c r="D44">
-        <v>9391.478999999999</v>
+        <v>17151.756</v>
       </c>
       <c r="E44">
-        <v>23150.484</v>
+        <v>29673.792</v>
       </c>
       <c r="F44">
-        <v>28428.292</v>
+        <v>40722.331</v>
       </c>
       <c r="G44">
-        <v>16936.968</v>
+        <v>29744.37</v>
       </c>
       <c r="H44">
-        <v>42134.79</v>
+        <v>51812.416</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>3781969180.674</v>
+        <v>5415140249.721</v>
       </c>
       <c r="M44">
-        <v>2248513604.1</v>
+        <v>3954314329.938</v>
       </c>
       <c r="N44">
-        <v>5606316529.621</v>
+        <v>6899380228.436</v>
       </c>
     </row>
     <row r="45">
@@ -2498,26 +2498,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C45">
-        <v>35859.163</v>
+        <v>25162.563</v>
       </c>
       <c r="D45">
-        <v>22604.22</v>
+        <v>18522.648</v>
       </c>
       <c r="E45">
-        <v>51334.498</v>
+        <v>31768.519</v>
       </c>
       <c r="F45">
-        <v>57022.372</v>
+        <v>36557.24</v>
       </c>
       <c r="G45">
-        <v>35836.885</v>
+        <v>26953.61</v>
       </c>
       <c r="H45">
-        <v>81970.068</v>
+        <v>46308.683</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2529,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>7587642978.428</v>
+        <v>4863805669.602</v>
       </c>
       <c r="M45">
-        <v>4763829616.074</v>
+        <v>3578760872.364</v>
       </c>
       <c r="N45">
-        <v>10912951614.14</v>
+        <v>6164041714.669</v>
       </c>
     </row>
     <row r="46">
@@ -2546,26 +2546,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C46">
-        <v>42012.756</v>
+        <v>24138.468</v>
       </c>
       <c r="D46">
-        <v>26174.23</v>
+        <v>17774.351</v>
       </c>
       <c r="E46">
-        <v>60441.672</v>
+        <v>30429.937</v>
       </c>
       <c r="F46">
-        <v>54630.086</v>
+        <v>28309.544</v>
       </c>
       <c r="G46">
-        <v>34094.913</v>
+        <v>20770.398</v>
       </c>
       <c r="H46">
-        <v>78722.342</v>
+        <v>35844.678</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2577,13 +2577,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>7262928011.096</v>
+        <v>3765711847.343</v>
       </c>
       <c r="M46">
-        <v>4533896843.822</v>
+        <v>2762638638.337</v>
       </c>
       <c r="N46">
-        <v>10480266032.26</v>
+        <v>4767961726.045</v>
       </c>
     </row>
     <row r="47">
@@ -2594,26 +2594,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C47">
-        <v>24358.308</v>
+        <v>23304.597</v>
       </c>
       <c r="D47">
-        <v>15395.543</v>
+        <v>17243.205</v>
       </c>
       <c r="E47">
-        <v>34890.458</v>
+        <v>29292.034</v>
       </c>
       <c r="F47">
-        <v>24522.782</v>
+        <v>19973.144</v>
       </c>
       <c r="G47">
-        <v>15421.869</v>
+        <v>14706.814</v>
       </c>
       <c r="H47">
-        <v>35162.31</v>
+        <v>25173.255</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>3257028031.666</v>
+        <v>2655662625.285</v>
       </c>
       <c r="M47">
-        <v>2043837196.652</v>
+        <v>1955174243.486</v>
       </c>
       <c r="N47">
-        <v>4683277736.371</v>
+        <v>3350531530.202</v>
       </c>
     </row>
     <row r="48">
@@ -2642,26 +2642,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>60-69</t>
         </is>
       </c>
       <c r="C48">
-        <v>36696.251</v>
+        <v>28272.936</v>
       </c>
       <c r="D48">
-        <v>23741.537</v>
+        <v>21106.583</v>
       </c>
       <c r="E48">
-        <v>51851.042</v>
+        <v>35200.665</v>
       </c>
       <c r="F48">
-        <v>26340.887</v>
+        <v>16379.063</v>
       </c>
       <c r="G48">
-        <v>16936.908</v>
+        <v>12173.94</v>
       </c>
       <c r="H48">
-        <v>37416.837</v>
+        <v>20394.664</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>3502827893.821</v>
+        <v>2177011128.886</v>
       </c>
       <c r="M48">
-        <v>2250181569.693</v>
+        <v>1618904141.11</v>
       </c>
       <c r="N48">
-        <v>4980751203.073</v>
+        <v>2713230846.196</v>
       </c>
     </row>
     <row r="49">
@@ -2690,26 +2690,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>65-75</t>
+          <t>70-79</t>
         </is>
       </c>
       <c r="C49">
-        <v>21794.189</v>
+        <v>18923.898</v>
       </c>
       <c r="D49">
-        <v>14112.31</v>
+        <v>14045.317</v>
       </c>
       <c r="E49">
-        <v>30814.826</v>
+        <v>23706.462</v>
       </c>
       <c r="F49">
-        <v>9581.915999999999</v>
+        <v>5755.786</v>
       </c>
       <c r="G49">
-        <v>6160.599</v>
+        <v>4241.729</v>
       </c>
       <c r="H49">
-        <v>13601.732</v>
+        <v>7268.338</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1275819844.746</v>
+        <v>765490881.844</v>
       </c>
       <c r="M49">
-        <v>819037428.095</v>
+        <v>565124169.132</v>
       </c>
       <c r="N49">
-        <v>1808044493.008</v>
+        <v>965787549.9809999</v>
       </c>
     </row>
     <row r="50">
@@ -2738,26 +2738,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>75-89</t>
+          <t>80-89</t>
         </is>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>8262.442999999999</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>6020.759</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>10542.876</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>449.858</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>314.099</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>599.728</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2769,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>59824524.616</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>41875237.468</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>79665220.56299999</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_age.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -447,13 +447,13 @@
         <v>527.673</v>
       </c>
       <c r="F2">
-        <v>4274.065</v>
+        <v>25644.389</v>
       </c>
       <c r="G2">
-        <v>3556.932</v>
+        <v>21341.592</v>
       </c>
       <c r="H2">
-        <v>5024.591</v>
+        <v>30147.548</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>568323919.3099999</v>
+        <v>3409943515.859</v>
       </c>
       <c r="M2">
-        <v>472974949.987</v>
+        <v>2837849699.921</v>
       </c>
       <c r="N2">
-        <v>668190075.255</v>
+        <v>4009140451.53</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1002.421</v>
       </c>
       <c r="F3">
-        <v>6681.877</v>
+        <v>40091.262</v>
       </c>
       <c r="G3">
-        <v>5644.158</v>
+        <v>33864.946</v>
       </c>
       <c r="H3">
-        <v>7767.589</v>
+        <v>46605.536</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>888997513.066</v>
+        <v>5333985078.396</v>
       </c>
       <c r="M3">
-        <v>750304219.4299999</v>
+        <v>4501825316.58</v>
       </c>
       <c r="N3">
-        <v>1033320642.738</v>
+        <v>6199923856.427</v>
       </c>
     </row>
     <row r="4">
@@ -543,13 +543,13 @@
         <v>2656.641</v>
       </c>
       <c r="F4">
-        <v>14151.994</v>
+        <v>84911.965</v>
       </c>
       <c r="G4">
-        <v>11967.93</v>
+        <v>71807.577</v>
       </c>
       <c r="H4">
-        <v>16430.584</v>
+        <v>98583.505</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1883184561.865</v>
+        <v>11299107371.188</v>
       </c>
       <c r="M4">
-        <v>1591019391.073</v>
+        <v>9546116346.438999</v>
       </c>
       <c r="N4">
-        <v>2186090301.067</v>
+        <v>13116541806.403</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>5663.309</v>
       </c>
       <c r="F5">
-        <v>21940.315</v>
+        <v>131641.889</v>
       </c>
       <c r="G5">
-        <v>18540.011</v>
+        <v>111240.066</v>
       </c>
       <c r="H5">
-        <v>25392.954</v>
+        <v>152357.727</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2917885424.216</v>
+        <v>17507312545.294</v>
       </c>
       <c r="M5">
-        <v>2466906659.924</v>
+        <v>14801439959.543</v>
       </c>
       <c r="N5">
-        <v>3375720380.454</v>
+        <v>20254322282.726</v>
       </c>
     </row>
     <row r="6">
@@ -639,13 +639,13 @@
         <v>12025.528</v>
       </c>
       <c r="F6">
-        <v>29710.038</v>
+        <v>178260.228</v>
       </c>
       <c r="G6">
-        <v>25235.649</v>
+        <v>151413.894</v>
       </c>
       <c r="H6">
-        <v>34197.946</v>
+        <v>205187.678</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3950490237.81</v>
+        <v>23702941426.859</v>
       </c>
       <c r="M6">
-        <v>3359102390.041</v>
+        <v>20154614340.247</v>
       </c>
       <c r="N6">
-        <v>4548095319.839</v>
+        <v>27288571919.033</v>
       </c>
     </row>
     <row r="7">
@@ -687,13 +687,13 @@
         <v>19484.179</v>
       </c>
       <c r="F7">
-        <v>20716.864</v>
+        <v>124301.186</v>
       </c>
       <c r="G7">
-        <v>17522.823</v>
+        <v>105136.939</v>
       </c>
       <c r="H7">
-        <v>23948.841</v>
+        <v>143693.048</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2754960868.613</v>
+        <v>16529765211.68</v>
       </c>
       <c r="M7">
-        <v>2328803769.141</v>
+        <v>13972822614.846</v>
       </c>
       <c r="N7">
-        <v>3185151124.847</v>
+        <v>19110906749.08</v>
       </c>
     </row>
     <row r="8">
@@ -735,13 +735,13 @@
         <v>26980.957</v>
       </c>
       <c r="F8">
-        <v>3320.724</v>
+        <v>19924.343</v>
       </c>
       <c r="G8">
-        <v>2654.717</v>
+        <v>15928.303</v>
       </c>
       <c r="H8">
-        <v>4051.753</v>
+        <v>24310.52</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>441545724.466</v>
+        <v>2649274346.794</v>
       </c>
       <c r="M8">
-        <v>352800943.056</v>
+        <v>2116805658.334</v>
       </c>
       <c r="N8">
-        <v>539025476.892</v>
+        <v>3234152861.353</v>
       </c>
     </row>
     <row r="9">
@@ -783,13 +783,13 @@
         <v>312.373</v>
       </c>
       <c r="F9">
-        <v>142.645</v>
+        <v>855.591</v>
       </c>
       <c r="G9">
-        <v>87.962</v>
+        <v>527.991</v>
       </c>
       <c r="H9">
-        <v>196.522</v>
+        <v>1179.739</v>
       </c>
       <c r="I9">
         <v>12624668.187</v>
@@ -801,13 +801,13 @@
         <v>17385898.071</v>
       </c>
       <c r="L9">
-        <v>18977742.602</v>
+        <v>113817319.979</v>
       </c>
       <c r="M9">
-        <v>11674435.013</v>
+        <v>70137154.457</v>
       </c>
       <c r="N9">
-        <v>26118885.61</v>
+        <v>156787452.254</v>
       </c>
     </row>
     <row r="10">
@@ -831,13 +831,13 @@
         <v>659.207</v>
       </c>
       <c r="F10">
-        <v>247.822</v>
+        <v>1486.129</v>
       </c>
       <c r="G10">
-        <v>155.132</v>
+        <v>931.367</v>
       </c>
       <c r="H10">
-        <v>338.704</v>
+        <v>2034.261</v>
       </c>
       <c r="I10">
         <v>26791010.955</v>
@@ -849,13 +849,13 @@
         <v>36750028.481</v>
       </c>
       <c r="L10">
-        <v>32954795.795</v>
+        <v>197611734.379</v>
       </c>
       <c r="M10">
-        <v>20646419.903</v>
+        <v>123876840.376</v>
       </c>
       <c r="N10">
-        <v>44994860.097</v>
+        <v>270352749.002</v>
       </c>
     </row>
     <row r="11">
@@ -879,13 +879,13 @@
         <v>2142.644</v>
       </c>
       <c r="F11">
-        <v>641.8200000000001</v>
+        <v>3848.786</v>
       </c>
       <c r="G11">
-        <v>399.698</v>
+        <v>2396.027</v>
       </c>
       <c r="H11">
-        <v>882.259</v>
+        <v>5292.254</v>
       </c>
       <c r="I11">
         <v>86862575.758</v>
@@ -897,13 +897,13 @@
         <v>119437917.617</v>
       </c>
       <c r="L11">
-        <v>85328318.935</v>
+        <v>511748478.946</v>
       </c>
       <c r="M11">
-        <v>53111722.416</v>
+        <v>318715096.025</v>
       </c>
       <c r="N11">
-        <v>117228310.514</v>
+        <v>703408777.789</v>
       </c>
     </row>
     <row r="12">
@@ -927,13 +927,13 @@
         <v>5322.98</v>
       </c>
       <c r="F12">
-        <v>1154.881</v>
+        <v>6929.31</v>
       </c>
       <c r="G12">
-        <v>719.85</v>
+        <v>4322.82</v>
       </c>
       <c r="H12">
-        <v>1577.98</v>
+        <v>9468.286</v>
       </c>
       <c r="I12">
         <v>217175593.428</v>
@@ -945,13 +945,13 @@
         <v>296551668.02</v>
       </c>
       <c r="L12">
-        <v>153570403.495</v>
+        <v>921429834.396</v>
       </c>
       <c r="M12">
-        <v>95723178.389</v>
+        <v>574843287.714</v>
       </c>
       <c r="N12">
-        <v>209678945.791</v>
+        <v>1257476441.088</v>
       </c>
     </row>
     <row r="13">
@@ -975,13 +975,13 @@
         <v>15019.866</v>
       </c>
       <c r="F13">
-        <v>2145.669</v>
+        <v>12869.55</v>
       </c>
       <c r="G13">
-        <v>1367.447</v>
+        <v>8208.856</v>
       </c>
       <c r="H13">
-        <v>2887.826</v>
+        <v>17324.296</v>
       </c>
       <c r="I13">
         <v>621559543.668</v>
@@ -993,13 +993,13 @@
         <v>836743352.5829999</v>
       </c>
       <c r="L13">
-        <v>285356608.735</v>
+        <v>1711898354.545</v>
       </c>
       <c r="M13">
-        <v>181946455.915</v>
+        <v>1092685341.354</v>
       </c>
       <c r="N13">
-        <v>384012357.243</v>
+        <v>2304339414.343</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>18155.831</v>
       </c>
       <c r="F14">
-        <v>1265.924</v>
+        <v>7598.197</v>
       </c>
       <c r="G14">
-        <v>788.644</v>
+        <v>4733.591</v>
       </c>
       <c r="H14">
-        <v>1728.698</v>
+        <v>10361.89</v>
       </c>
       <c r="I14">
         <v>743024097.918</v>
@@ -1041,13 +1041,13 @@
         <v>1012396149.154</v>
       </c>
       <c r="L14">
-        <v>168339263.48</v>
+        <v>1010498677.623</v>
       </c>
       <c r="M14">
-        <v>104968881.445</v>
+        <v>629801007.13</v>
       </c>
       <c r="N14">
-        <v>229648465.201</v>
+        <v>1376612189.813</v>
       </c>
     </row>
     <row r="15">
@@ -1071,13 +1071,13 @@
         <v>12113.072</v>
       </c>
       <c r="F15">
-        <v>122.629</v>
+        <v>736.763</v>
       </c>
       <c r="G15">
-        <v>72.34999999999999</v>
+        <v>434.384</v>
       </c>
       <c r="H15">
-        <v>176.202</v>
+        <v>1059.145</v>
       </c>
       <c r="I15">
         <v>485254186.821</v>
@@ -1089,19 +1089,19 @@
         <v>674286819.957</v>
       </c>
       <c r="L15">
-        <v>16294216.201</v>
+        <v>97900029.102</v>
       </c>
       <c r="M15">
-        <v>9649085.187000001</v>
+        <v>57905861.696</v>
       </c>
       <c r="N15">
-        <v>23420968.231</v>
+        <v>140774913.556</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1110,46 +1110,46 @@
         </is>
       </c>
       <c r="C16">
-        <v>6.528</v>
+        <v>1894.309</v>
       </c>
       <c r="D16">
-        <v>0.166</v>
+        <v>51.38</v>
       </c>
       <c r="E16">
-        <v>13.247</v>
+        <v>3758.533</v>
       </c>
       <c r="F16">
-        <v>4.534</v>
+        <v>6350.458</v>
       </c>
       <c r="G16">
-        <v>0.116</v>
+        <v>172.84</v>
       </c>
       <c r="H16">
-        <v>9.247999999999999</v>
+        <v>12633.573</v>
       </c>
       <c r="I16">
-        <v>287831.257</v>
+        <v>28029471.882</v>
       </c>
       <c r="J16">
-        <v>7277.481</v>
+        <v>756475.393</v>
       </c>
       <c r="K16">
-        <v>583349.034</v>
+        <v>55534309.393</v>
       </c>
       <c r="L16">
-        <v>603332.035</v>
+        <v>845502314.85</v>
       </c>
       <c r="M16">
-        <v>15268.137</v>
+        <v>22826350.185</v>
       </c>
       <c r="N16">
-        <v>1226370.443</v>
+        <v>1676578080.297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1158,46 +1158,46 @@
         </is>
       </c>
       <c r="C17">
-        <v>60.959</v>
+        <v>3254.471</v>
       </c>
       <c r="D17">
-        <v>1.479</v>
+        <v>81.848</v>
       </c>
       <c r="E17">
-        <v>121.819</v>
+        <v>6445.208</v>
       </c>
       <c r="F17">
-        <v>35.977</v>
+        <v>9146.734</v>
       </c>
       <c r="G17">
-        <v>0.874</v>
+        <v>227.879</v>
       </c>
       <c r="H17">
-        <v>72.148</v>
+        <v>18175.363</v>
       </c>
       <c r="I17">
-        <v>2684399.428</v>
+        <v>48146712.912</v>
       </c>
       <c r="J17">
-        <v>65194.105</v>
+        <v>1206667.408</v>
       </c>
       <c r="K17">
-        <v>5374154.762</v>
+        <v>95498379.02599999</v>
       </c>
       <c r="L17">
-        <v>4790454.453</v>
+        <v>1217080977.606</v>
       </c>
       <c r="M17">
-        <v>116207.783</v>
+        <v>30178413.96</v>
       </c>
       <c r="N17">
-        <v>9608915.275</v>
+        <v>2419169596.938</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C18">
-        <v>166.366</v>
+        <v>4228.092</v>
       </c>
       <c r="D18">
-        <v>4.607</v>
+        <v>119.466</v>
       </c>
       <c r="E18">
-        <v>330.471</v>
+        <v>8345.164000000001</v>
       </c>
       <c r="F18">
-        <v>81.111</v>
+        <v>9596.561</v>
       </c>
       <c r="G18">
-        <v>2.223</v>
+        <v>268.35</v>
       </c>
       <c r="H18">
-        <v>161.129</v>
+        <v>18979.125</v>
       </c>
       <c r="I18">
-        <v>7336283.522</v>
+        <v>62603350.387</v>
       </c>
       <c r="J18">
-        <v>204331.269</v>
+        <v>1788713.647</v>
       </c>
       <c r="K18">
-        <v>14577786.057</v>
+        <v>123587550.838</v>
       </c>
       <c r="L18">
-        <v>10788509.07</v>
+        <v>1276751642.829</v>
       </c>
       <c r="M18">
-        <v>297297.215</v>
+        <v>35853933.602</v>
       </c>
       <c r="N18">
-        <v>21485336.77</v>
+        <v>2530252516.863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1254,46 +1254,46 @@
         </is>
       </c>
       <c r="C19">
-        <v>253.651</v>
+        <v>5660.605</v>
       </c>
       <c r="D19">
-        <v>6.417</v>
+        <v>145.171</v>
       </c>
       <c r="E19">
-        <v>502.503</v>
+        <v>11151.976</v>
       </c>
       <c r="F19">
-        <v>91.673</v>
+        <v>9230.322</v>
       </c>
       <c r="G19">
-        <v>2.338</v>
+        <v>238.609</v>
       </c>
       <c r="H19">
-        <v>181.907</v>
+        <v>18228.128</v>
       </c>
       <c r="I19">
-        <v>11170708.678</v>
+        <v>83720438.985</v>
       </c>
       <c r="J19">
-        <v>284993.289</v>
+        <v>2167553.908</v>
       </c>
       <c r="K19">
-        <v>22174509.11</v>
+        <v>165145381.579</v>
       </c>
       <c r="L19">
-        <v>12192208.892</v>
+        <v>1227915679.66</v>
       </c>
       <c r="M19">
-        <v>312048.219</v>
+        <v>31844117.762</v>
       </c>
       <c r="N19">
-        <v>24148334.836</v>
+        <v>2421276503.747</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1302,46 +1302,46 @@
         </is>
       </c>
       <c r="C20">
-        <v>369.148</v>
+        <v>8149.361</v>
       </c>
       <c r="D20">
-        <v>8.140000000000001</v>
+        <v>174.067</v>
       </c>
       <c r="E20">
-        <v>730.418</v>
+        <v>16089.132</v>
       </c>
       <c r="F20">
-        <v>93.142</v>
+        <v>8671.566000000001</v>
       </c>
       <c r="G20">
-        <v>2.03</v>
+        <v>187.182</v>
       </c>
       <c r="H20">
-        <v>184.113</v>
+        <v>17123.449</v>
       </c>
       <c r="I20">
-        <v>16292320.395</v>
+        <v>120770354.888</v>
       </c>
       <c r="J20">
-        <v>359569.578</v>
+        <v>2585887.498</v>
       </c>
       <c r="K20">
-        <v>32204944.651</v>
+        <v>238023630.565</v>
       </c>
       <c r="L20">
-        <v>12378308.871</v>
+        <v>1152489081.259</v>
       </c>
       <c r="M20">
-        <v>270008.566</v>
+        <v>24831189.942</v>
       </c>
       <c r="N20">
-        <v>24515074.352</v>
+        <v>2277434714.906</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1350,46 +1350,46 @@
         </is>
       </c>
       <c r="C21">
-        <v>274.784</v>
+        <v>5396.504</v>
       </c>
       <c r="D21">
-        <v>7.11</v>
+        <v>136.607</v>
       </c>
       <c r="E21">
-        <v>543.36</v>
+        <v>10637.601</v>
       </c>
       <c r="F21">
-        <v>39.948</v>
+        <v>2736.496</v>
       </c>
       <c r="G21">
-        <v>0.988</v>
+        <v>67.95</v>
       </c>
       <c r="H21">
-        <v>79.185</v>
+        <v>5389.557</v>
       </c>
       <c r="I21">
-        <v>12127656.813</v>
+        <v>79963596.814</v>
       </c>
       <c r="J21">
-        <v>312238.422</v>
+        <v>2010396.587</v>
       </c>
       <c r="K21">
-        <v>23906849.607</v>
+        <v>157103022.368</v>
       </c>
       <c r="L21">
-        <v>5319096.246</v>
+        <v>364299715.718</v>
       </c>
       <c r="M21">
-        <v>131065.823</v>
+        <v>9054917.365</v>
       </c>
       <c r="N21">
-        <v>10538861.263</v>
+        <v>717828163.495</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1398,46 +1398,46 @@
         </is>
       </c>
       <c r="C22">
-        <v>124.355</v>
+        <v>2147.623</v>
       </c>
       <c r="D22">
-        <v>4.074</v>
+        <v>66.908</v>
       </c>
       <c r="E22">
-        <v>247.321</v>
+        <v>4272.897</v>
       </c>
       <c r="F22">
-        <v>3.616</v>
+        <v>146.963</v>
       </c>
       <c r="G22">
-        <v>0.113</v>
+        <v>4.621</v>
       </c>
       <c r="H22">
-        <v>7.317</v>
+        <v>297.448</v>
       </c>
       <c r="I22">
-        <v>5481398.38</v>
+        <v>31794401.824</v>
       </c>
       <c r="J22">
-        <v>180272.451</v>
+        <v>993816.917</v>
       </c>
       <c r="K22">
-        <v>10913752.311</v>
+        <v>63325143.598</v>
       </c>
       <c r="L22">
-        <v>480983.852</v>
+        <v>19555487.982</v>
       </c>
       <c r="M22">
-        <v>15086.521</v>
+        <v>617072.436</v>
       </c>
       <c r="N22">
-        <v>974218.181</v>
+        <v>39594743.032</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1446,46 +1446,46 @@
         </is>
       </c>
       <c r="C23">
-        <v>1893.606</v>
+        <v>399.399</v>
       </c>
       <c r="D23">
-        <v>51.513</v>
+        <v>1.347</v>
       </c>
       <c r="E23">
-        <v>3757.498</v>
+        <v>758.071</v>
       </c>
       <c r="F23">
-        <v>1058.77</v>
+        <v>1607.241</v>
       </c>
       <c r="G23">
-        <v>29.067</v>
+        <v>5.43</v>
       </c>
       <c r="H23">
-        <v>2101.267</v>
+        <v>3051.842</v>
       </c>
       <c r="I23">
-        <v>28035782.581</v>
+        <v>30045779.207</v>
       </c>
       <c r="J23">
-        <v>760395.046</v>
+        <v>102747.326</v>
       </c>
       <c r="K23">
-        <v>55477424.976</v>
+        <v>57094246.424</v>
       </c>
       <c r="L23">
-        <v>140823281.175</v>
+        <v>213955165.424</v>
       </c>
       <c r="M23">
-        <v>3798594.882</v>
+        <v>786541.1899999999</v>
       </c>
       <c r="N23">
-        <v>279883284.782</v>
+        <v>406191666.442</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1494,46 +1494,46 @@
         </is>
       </c>
       <c r="C24">
-        <v>3253.802</v>
+        <v>649.722</v>
       </c>
       <c r="D24">
-        <v>81.538</v>
+        <v>-0.217</v>
       </c>
       <c r="E24">
-        <v>6454.539</v>
+        <v>1228.729</v>
       </c>
       <c r="F24">
-        <v>1526.314</v>
+        <v>2147.952</v>
       </c>
       <c r="G24">
-        <v>38.168</v>
+        <v>-1.338</v>
       </c>
       <c r="H24">
-        <v>3023.812</v>
+        <v>4070.832</v>
       </c>
       <c r="I24">
-        <v>48159696.811</v>
+        <v>48844902.078</v>
       </c>
       <c r="J24">
-        <v>1215253.56</v>
+        <v>-24980.693</v>
       </c>
       <c r="K24">
-        <v>95551590.322</v>
+        <v>92307990.48199999</v>
       </c>
       <c r="L24">
-        <v>202857513.568</v>
+        <v>285895284.161</v>
       </c>
       <c r="M24">
-        <v>5035584.071</v>
+        <v>-176524.007</v>
       </c>
       <c r="N24">
-        <v>402948266.95</v>
+        <v>541325512.415</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1542,46 +1542,46 @@
         </is>
       </c>
       <c r="C25">
-        <v>4227.728</v>
+        <v>947.361</v>
       </c>
       <c r="D25">
-        <v>120.298</v>
+        <v>1.343</v>
       </c>
       <c r="E25">
-        <v>8355.91</v>
+        <v>1801.183</v>
       </c>
       <c r="F25">
-        <v>1601.907</v>
+        <v>2504.879</v>
       </c>
       <c r="G25">
-        <v>45.054</v>
+        <v>2.636</v>
       </c>
       <c r="H25">
-        <v>3169.984</v>
+        <v>4748.063</v>
       </c>
       <c r="I25">
-        <v>62609464.61</v>
+        <v>71245032.785</v>
       </c>
       <c r="J25">
-        <v>1778342.734</v>
+        <v>97333.23299999999</v>
       </c>
       <c r="K25">
-        <v>123778116.781</v>
+        <v>135578262.459</v>
       </c>
       <c r="L25">
-        <v>212766369.544</v>
+        <v>332931567.664</v>
       </c>
       <c r="M25">
-        <v>5958834.509</v>
+        <v>329251.616</v>
       </c>
       <c r="N25">
-        <v>421613253.085</v>
+        <v>632051897.163</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1590,46 +1590,46 @@
         </is>
       </c>
       <c r="C26">
-        <v>5657.545</v>
+        <v>1556.363</v>
       </c>
       <c r="D26">
-        <v>145.697</v>
+        <v>0.347</v>
       </c>
       <c r="E26">
-        <v>11145.373</v>
+        <v>2935.864</v>
       </c>
       <c r="F26">
-        <v>1537.868</v>
+        <v>2974.387</v>
       </c>
       <c r="G26">
-        <v>39.705</v>
+        <v>3.443</v>
       </c>
       <c r="H26">
-        <v>3030.738</v>
+        <v>5597.283</v>
       </c>
       <c r="I26">
-        <v>83730258.132</v>
+        <v>117024736.045</v>
       </c>
       <c r="J26">
-        <v>2155523.109</v>
+        <v>-3392.35</v>
       </c>
       <c r="K26">
-        <v>165003196.556</v>
+        <v>220752398.165</v>
       </c>
       <c r="L26">
-        <v>204402592.641</v>
+        <v>396042884.154</v>
       </c>
       <c r="M26">
-        <v>5272398.716</v>
+        <v>345568.794</v>
       </c>
       <c r="N26">
-        <v>403342662.181</v>
+        <v>744380598.283</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1638,46 +1638,46 @@
         </is>
       </c>
       <c r="C27">
-        <v>8151.597</v>
+        <v>2204.451</v>
       </c>
       <c r="D27">
-        <v>174.203</v>
+        <v>-5.371</v>
       </c>
       <c r="E27">
-        <v>16073.025</v>
+        <v>4098.926</v>
       </c>
       <c r="F27">
-        <v>1443.589</v>
+        <v>2882.624</v>
       </c>
       <c r="G27">
-        <v>31.053</v>
+        <v>-5.598</v>
       </c>
       <c r="H27">
-        <v>2853.306</v>
+        <v>5350.219</v>
       </c>
       <c r="I27">
-        <v>120745802.531</v>
+        <v>165840324.827</v>
       </c>
       <c r="J27">
-        <v>2578842.798</v>
+        <v>-442828.566</v>
       </c>
       <c r="K27">
-        <v>238044167.037</v>
+        <v>307754750.43</v>
       </c>
       <c r="L27">
-        <v>192127118.108</v>
+        <v>383225266.933</v>
       </c>
       <c r="M27">
-        <v>4128126.927</v>
+        <v>-619752.483</v>
       </c>
       <c r="N27">
-        <v>379903751.165</v>
+        <v>711552226.528</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1686,46 +1686,46 @@
         </is>
       </c>
       <c r="C28">
-        <v>5404.212</v>
+        <v>701.866</v>
       </c>
       <c r="D28">
-        <v>135.927</v>
+        <v>1.871</v>
       </c>
       <c r="E28">
-        <v>10630.46</v>
+        <v>1318.325</v>
       </c>
       <c r="F28">
-        <v>456.439</v>
+        <v>509.639</v>
       </c>
       <c r="G28">
-        <v>11.311</v>
+        <v>1.836</v>
       </c>
       <c r="H28">
-        <v>898.789</v>
+        <v>958.568</v>
       </c>
       <c r="I28">
-        <v>80011681.31200001</v>
+        <v>52777077.836</v>
       </c>
       <c r="J28">
-        <v>2009896.933</v>
+        <v>139091.574</v>
       </c>
       <c r="K28">
-        <v>157493290.229</v>
+        <v>99000568.7</v>
       </c>
       <c r="L28">
-        <v>60687650.993</v>
+        <v>67774076.956</v>
       </c>
       <c r="M28">
-        <v>1506109.587</v>
+        <v>240238.285</v>
       </c>
       <c r="N28">
-        <v>119631520.449</v>
+        <v>127707927.415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1734,46 +1734,46 @@
         </is>
       </c>
       <c r="C29">
-        <v>2147.808</v>
+        <v>28.587</v>
       </c>
       <c r="D29">
-        <v>67.083</v>
+        <v>-0.056</v>
       </c>
       <c r="E29">
-        <v>4271.429</v>
+        <v>54.835</v>
       </c>
       <c r="F29">
-        <v>24.501</v>
+        <v>3.734</v>
       </c>
       <c r="G29">
-        <v>0.771</v>
+        <v>0.023</v>
       </c>
       <c r="H29">
-        <v>49.678</v>
+        <v>7.382</v>
       </c>
       <c r="I29">
-        <v>31810009.392</v>
+        <v>2148048.83</v>
       </c>
       <c r="J29">
-        <v>995211.5919999999</v>
+        <v>-4280.982</v>
       </c>
       <c r="K29">
-        <v>63210546.572</v>
+        <v>4125877.418</v>
       </c>
       <c r="L29">
-        <v>3256849.302</v>
+        <v>496537.646</v>
       </c>
       <c r="M29">
-        <v>100910.075</v>
+        <v>3157.453</v>
       </c>
       <c r="N29">
-        <v>6579510.53</v>
+        <v>982867.316</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1782,46 +1782,46 @@
         </is>
       </c>
       <c r="C30">
-        <v>399.407</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1.457</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>757.808</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>268.166</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>1.065</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>507.387</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>30062019.509</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>103798.479</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>56994575.396</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>35644159.674</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>131637.483</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>67555539.222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1830,46 +1830,46 @@
         </is>
       </c>
       <c r="C31">
-        <v>649.215</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>-0.377</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1231.07</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>357.955</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>-0.214</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>676.266</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>48849817.705</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>-42707.906</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>92447549.846</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>47590943.91</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>-23157.682</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>90013995.711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1878,46 +1878,46 @@
         </is>
       </c>
       <c r="C32">
-        <v>947.6559999999999</v>
+        <v>141.847</v>
       </c>
       <c r="D32">
-        <v>1.237</v>
+        <v>103.441</v>
       </c>
       <c r="E32">
-        <v>1800.993</v>
+        <v>179.849</v>
       </c>
       <c r="F32">
-        <v>417.229</v>
+        <v>1120.769</v>
       </c>
       <c r="G32">
-        <v>0.359</v>
+        <v>816.599</v>
       </c>
       <c r="H32">
-        <v>792.061</v>
+        <v>1420.768</v>
       </c>
       <c r="I32">
-        <v>71270875.506</v>
+        <v>2388181.845</v>
       </c>
       <c r="J32">
-        <v>80298.06200000001</v>
+        <v>1740169.747</v>
       </c>
       <c r="K32">
-        <v>135527906.052</v>
+        <v>3027325.874</v>
       </c>
       <c r="L32">
-        <v>55432896.002</v>
+        <v>149084333.298</v>
       </c>
       <c r="M32">
-        <v>55668.372</v>
+        <v>108451704.62</v>
       </c>
       <c r="N32">
-        <v>105298072.637</v>
+        <v>188793462.826</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1926,46 +1926,46 @@
         </is>
       </c>
       <c r="C33">
-        <v>1558.278</v>
+        <v>315.011</v>
       </c>
       <c r="D33">
-        <v>0.03</v>
+        <v>229.466</v>
       </c>
       <c r="E33">
-        <v>2934.976</v>
+        <v>398.979</v>
       </c>
       <c r="F33">
-        <v>495.826</v>
+        <v>1853.366</v>
       </c>
       <c r="G33">
-        <v>0.249</v>
+        <v>1350.52</v>
       </c>
       <c r="H33">
-        <v>934.796</v>
+        <v>2347.496</v>
       </c>
       <c r="I33">
-        <v>117078479.506</v>
+        <v>5304600.941</v>
       </c>
       <c r="J33">
-        <v>-10491.586</v>
+        <v>3859664.153</v>
       </c>
       <c r="K33">
-        <v>220509631.404</v>
+        <v>6718529.145</v>
       </c>
       <c r="L33">
-        <v>65894562.362</v>
+        <v>246556744.708</v>
       </c>
       <c r="M33">
-        <v>44245.237</v>
+        <v>179511024.497</v>
       </c>
       <c r="N33">
-        <v>124162396.011</v>
+        <v>312474773.371</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1974,46 +1974,46 @@
         </is>
       </c>
       <c r="C34">
-        <v>2204.605</v>
+        <v>1748.878</v>
       </c>
       <c r="D34">
-        <v>-5.532</v>
+        <v>1280.755</v>
       </c>
       <c r="E34">
-        <v>4094.745</v>
+        <v>2199.489</v>
       </c>
       <c r="F34">
-        <v>479.357</v>
+        <v>6479.517</v>
       </c>
       <c r="G34">
-        <v>-0.756</v>
+        <v>4745.81</v>
       </c>
       <c r="H34">
-        <v>893.89</v>
+        <v>8155.813</v>
       </c>
       <c r="I34">
-        <v>165815067.825</v>
+        <v>29447424.355</v>
       </c>
       <c r="J34">
-        <v>-444855.056</v>
+        <v>21562828.935</v>
       </c>
       <c r="K34">
-        <v>307122763.708</v>
+        <v>37051718.534</v>
       </c>
       <c r="L34">
-        <v>63771708.795</v>
+        <v>861988167.091</v>
       </c>
       <c r="M34">
-        <v>-109218.477</v>
+        <v>631184504.4960001</v>
       </c>
       <c r="N34">
-        <v>118720647.762</v>
+        <v>1084833789.157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2022,46 +2022,46 @@
         </is>
       </c>
       <c r="C35">
-        <v>701.659</v>
+        <v>5029.086</v>
       </c>
       <c r="D35">
-        <v>1.575</v>
+        <v>3662.78</v>
       </c>
       <c r="E35">
-        <v>1317.802</v>
+        <v>6370.914</v>
       </c>
       <c r="F35">
-        <v>84.997</v>
+        <v>9307.517</v>
       </c>
       <c r="G35">
-        <v>0.237</v>
+        <v>6761.294</v>
       </c>
       <c r="H35">
-        <v>160.047</v>
+        <v>11803.707</v>
       </c>
       <c r="I35">
-        <v>52780173.004</v>
+        <v>84690101.65000001</v>
       </c>
       <c r="J35">
-        <v>133948.394</v>
+        <v>61562557.036</v>
       </c>
       <c r="K35">
-        <v>99192685.17</v>
+        <v>107261467.033</v>
       </c>
       <c r="L35">
-        <v>11302452.335</v>
+        <v>1238125280.644</v>
       </c>
       <c r="M35">
-        <v>33548.081</v>
+        <v>900887672.028</v>
       </c>
       <c r="N35">
-        <v>21296515.893</v>
+        <v>1570542068.676</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2070,46 +2070,46 @@
         </is>
       </c>
       <c r="C36">
-        <v>28.579</v>
+        <v>6166.63</v>
       </c>
       <c r="D36">
-        <v>-0.062</v>
+        <v>4443.369</v>
       </c>
       <c r="E36">
-        <v>54.914</v>
+        <v>7941.827</v>
       </c>
       <c r="F36">
-        <v>0.622</v>
+        <v>1832.354</v>
       </c>
       <c r="G36">
-        <v>0.004</v>
+        <v>1277.375</v>
       </c>
       <c r="H36">
-        <v>1.228</v>
+        <v>2445.067</v>
       </c>
       <c r="I36">
-        <v>2149369.664</v>
+        <v>103863482.394</v>
       </c>
       <c r="J36">
-        <v>-3488.04</v>
+        <v>74616549.62199999</v>
       </c>
       <c r="K36">
-        <v>4121347.329</v>
+        <v>133674076.938</v>
       </c>
       <c r="L36">
-        <v>82597.439</v>
+        <v>243741285.04</v>
       </c>
       <c r="M36">
-        <v>469.324</v>
+        <v>170136031.851</v>
       </c>
       <c r="N36">
-        <v>163299.989</v>
+        <v>324950859.627</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>23387.647</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>17188.944</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>29658.356</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>121996.268</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>88979.637</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>155525.393</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,19 +2145,19 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>16229129916.12</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>11839019659.059</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>20685795205.155</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>25158.741</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>18556.952</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>31748.339</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>109659.021</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>80550.38800000001</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>138954.357</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,19 +2193,19 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>14592475998.984</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>10697565816.967</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>18454415670.285</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2214,46 +2214,46 @@
         </is>
       </c>
       <c r="C39">
-        <v>141.923</v>
+        <v>24144.278</v>
       </c>
       <c r="D39">
-        <v>103.344</v>
+        <v>17787.377</v>
       </c>
       <c r="E39">
-        <v>179.963</v>
+        <v>30441.59</v>
       </c>
       <c r="F39">
-        <v>186.8</v>
+        <v>84932.38499999999</v>
       </c>
       <c r="G39">
-        <v>136.016</v>
+        <v>62354.164</v>
       </c>
       <c r="H39">
-        <v>236.889</v>
+        <v>107571.933</v>
       </c>
       <c r="I39">
-        <v>2387158.058</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1739787.77</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>3030234.512</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>24827215.072</v>
+        <v>11299084455.032</v>
       </c>
       <c r="M39">
-        <v>18121586.298</v>
+        <v>8297176118.243</v>
       </c>
       <c r="N39">
-        <v>31528160.226</v>
+        <v>14311334104.808</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,46 +2262,46 @@
         </is>
       </c>
       <c r="C40">
-        <v>314.967</v>
+        <v>23298.353</v>
       </c>
       <c r="D40">
-        <v>229.534</v>
+        <v>17252.268</v>
       </c>
       <c r="E40">
-        <v>399.041</v>
+        <v>29261.056</v>
       </c>
       <c r="F40">
-        <v>308.852</v>
+        <v>59981.172</v>
       </c>
       <c r="G40">
-        <v>224.868</v>
+        <v>44233.259</v>
       </c>
       <c r="H40">
-        <v>391.636</v>
+        <v>75394.673</v>
       </c>
       <c r="I40">
-        <v>5305909.929</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>3862149.184</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>6716388.387</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>41087178.267</v>
+        <v>7977280305.201</v>
       </c>
       <c r="M40">
-        <v>29897306.515</v>
+        <v>5883149286.631</v>
       </c>
       <c r="N40">
-        <v>52044326.903</v>
+        <v>10032016277.849</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2310,46 +2310,46 @@
         </is>
       </c>
       <c r="C41">
-        <v>1748.749</v>
+        <v>28266.288</v>
       </c>
       <c r="D41">
-        <v>1280.507</v>
+        <v>21099.4</v>
       </c>
       <c r="E41">
-        <v>2201.649</v>
+        <v>35240.32</v>
       </c>
       <c r="F41">
-        <v>1080.265</v>
+        <v>49060.557</v>
       </c>
       <c r="G41">
-        <v>790.23</v>
+        <v>36553.067</v>
       </c>
       <c r="H41">
-        <v>1359.475</v>
+        <v>61428.956</v>
       </c>
       <c r="I41">
-        <v>29442742.558</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>21593775.549</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>37062127.814</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>143676136.46</v>
+        <v>6525564151.06</v>
       </c>
       <c r="M41">
-        <v>105221327.299</v>
+        <v>4863644128.885</v>
       </c>
       <c r="N41">
-        <v>180810083.632</v>
+        <v>8166869931.232</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2358,46 +2358,46 @@
         </is>
       </c>
       <c r="C42">
-        <v>5032.179</v>
+        <v>18931.236</v>
       </c>
       <c r="D42">
-        <v>3661.669</v>
+        <v>14034.587</v>
       </c>
       <c r="E42">
-        <v>6366.488</v>
+        <v>23693.444</v>
       </c>
       <c r="F42">
-        <v>1551.952</v>
+        <v>17278.742</v>
       </c>
       <c r="G42">
-        <v>1128.399</v>
+        <v>12785.948</v>
       </c>
       <c r="H42">
-        <v>1968.797</v>
+        <v>21784.437</v>
       </c>
       <c r="I42">
-        <v>84709983.742</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>61599699.981</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>107246781.159</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>206376456.683</v>
+        <v>2298566905.923</v>
       </c>
       <c r="M42">
-        <v>149893138.985</v>
+        <v>1699841662.735</v>
       </c>
       <c r="N42">
-        <v>261862703.677</v>
+        <v>2897544293.618</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2406,376 +2406,40 @@
         </is>
       </c>
       <c r="C43">
-        <v>6168.568</v>
+        <v>8262.669</v>
       </c>
       <c r="D43">
-        <v>4434.475</v>
+        <v>6028.771</v>
       </c>
       <c r="E43">
-        <v>7938.561</v>
+        <v>10542.591</v>
       </c>
       <c r="F43">
-        <v>305.366</v>
+        <v>1349.688</v>
       </c>
       <c r="G43">
-        <v>213.528</v>
+        <v>947.4160000000001</v>
       </c>
       <c r="H43">
-        <v>406.978</v>
+        <v>1789.806</v>
       </c>
       <c r="I43">
-        <v>103863024.868</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>74749373.568</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>133572105.085</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>40604289.545</v>
+        <v>179472527.875</v>
       </c>
       <c r="M43">
-        <v>28405804.11</v>
+        <v>125589587.294</v>
       </c>
       <c r="N43">
-        <v>54236900.958</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>20-29</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>23393.237</v>
-      </c>
-      <c r="D44">
-        <v>17151.756</v>
-      </c>
-      <c r="E44">
-        <v>29673.792</v>
-      </c>
-      <c r="F44">
-        <v>40722.331</v>
-      </c>
-      <c r="G44">
-        <v>29744.37</v>
-      </c>
-      <c r="H44">
-        <v>51812.416</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>5415140249.721</v>
-      </c>
-      <c r="M44">
-        <v>3954314329.938</v>
-      </c>
-      <c r="N44">
-        <v>6899380228.436</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>30-39</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>25162.563</v>
-      </c>
-      <c r="D45">
-        <v>18522.648</v>
-      </c>
-      <c r="E45">
-        <v>31768.519</v>
-      </c>
-      <c r="F45">
-        <v>36557.24</v>
-      </c>
-      <c r="G45">
-        <v>26953.61</v>
-      </c>
-      <c r="H45">
-        <v>46308.683</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>4863805669.602</v>
-      </c>
-      <c r="M45">
-        <v>3578760872.364</v>
-      </c>
-      <c r="N45">
-        <v>6164041714.669</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>40-49</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>24138.468</v>
-      </c>
-      <c r="D46">
-        <v>17774.351</v>
-      </c>
-      <c r="E46">
-        <v>30429.937</v>
-      </c>
-      <c r="F46">
-        <v>28309.544</v>
-      </c>
-      <c r="G46">
-        <v>20770.398</v>
-      </c>
-      <c r="H46">
-        <v>35844.678</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>3765711847.343</v>
-      </c>
-      <c r="M46">
-        <v>2762638638.337</v>
-      </c>
-      <c r="N46">
-        <v>4767961726.045</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>50-59</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>23304.597</v>
-      </c>
-      <c r="D47">
-        <v>17243.205</v>
-      </c>
-      <c r="E47">
-        <v>29292.034</v>
-      </c>
-      <c r="F47">
-        <v>19973.144</v>
-      </c>
-      <c r="G47">
-        <v>14706.814</v>
-      </c>
-      <c r="H47">
-        <v>25173.255</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>2655662625.285</v>
-      </c>
-      <c r="M47">
-        <v>1955174243.486</v>
-      </c>
-      <c r="N47">
-        <v>3350531530.202</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>60-69</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>28272.936</v>
-      </c>
-      <c r="D48">
-        <v>21106.583</v>
-      </c>
-      <c r="E48">
-        <v>35200.665</v>
-      </c>
-      <c r="F48">
-        <v>16379.063</v>
-      </c>
-      <c r="G48">
-        <v>12173.94</v>
-      </c>
-      <c r="H48">
-        <v>20394.664</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>2177011128.886</v>
-      </c>
-      <c r="M48">
-        <v>1618904141.11</v>
-      </c>
-      <c r="N48">
-        <v>2713230846.196</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>70-79</t>
-        </is>
-      </c>
-      <c r="C49">
-        <v>18923.898</v>
-      </c>
-      <c r="D49">
-        <v>14045.317</v>
-      </c>
-      <c r="E49">
-        <v>23706.462</v>
-      </c>
-      <c r="F49">
-        <v>5755.786</v>
-      </c>
-      <c r="G49">
-        <v>4241.729</v>
-      </c>
-      <c r="H49">
-        <v>7268.338</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>765490881.844</v>
-      </c>
-      <c r="M49">
-        <v>565124169.132</v>
-      </c>
-      <c r="N49">
-        <v>965787549.9809999</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>80-89</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>8262.442999999999</v>
-      </c>
-      <c r="D50">
-        <v>6020.759</v>
-      </c>
-      <c r="E50">
-        <v>10542.876</v>
-      </c>
-      <c r="F50">
-        <v>449.858</v>
-      </c>
-      <c r="G50">
-        <v>314.099</v>
-      </c>
-      <c r="H50">
-        <v>599.728</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>59824524.616</v>
-      </c>
-      <c r="M50">
-        <v>41875237.468</v>
-      </c>
-      <c r="N50">
-        <v>79665220.56299999</v>
+        <v>238543013.056</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_age.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_age.xlsx
@@ -377,7 +377,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_sup</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -392,7 +392,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>tot_daly_sup</t>
+          <t>tot_daly_up</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>tot_medic_costs_sup</t>
+          <t>tot_medic_costs_up</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -422,7 +422,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>tot_soc_costs_sup</t>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
